--- a/MAM_Tool_Journal_Entries_Testing_PAT_2026YE.xlsx
+++ b/MAM_Tool_Journal_Entries_Testing_PAT_2026YE.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="58">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -396,6 +396,12 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1136,7 +1142,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="top"/>
@@ -1931,10 +1937,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -1942,6 +1944,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="2" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
       <protection locked="0" hidden="0"/>
@@ -1958,16 +1964,31 @@
       <alignment vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="6" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="34" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="55" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="53" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2043,6 +2064,9 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2804,15 +2828,15 @@
           <t>{a}</t>
         </is>
       </c>
-      <c r="B3" s="264" t="n"/>
-      <c r="C3" s="265" t="n"/>
-      <c r="D3" s="265" t="n"/>
-      <c r="E3" s="265" t="n"/>
-      <c r="F3" s="265" t="n"/>
-      <c r="G3" s="265" t="n"/>
-      <c r="H3" s="265" t="n"/>
-      <c r="I3" s="265" t="n"/>
-      <c r="J3" s="266" t="n"/>
+      <c r="B3" s="273" t="n"/>
+      <c r="C3" s="274" t="n"/>
+      <c r="D3" s="274" t="n"/>
+      <c r="E3" s="274" t="n"/>
+      <c r="F3" s="274" t="n"/>
+      <c r="G3" s="274" t="n"/>
+      <c r="H3" s="274" t="n"/>
+      <c r="I3" s="274" t="n"/>
+      <c r="J3" s="275" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>{a}</t>
@@ -2828,15 +2852,15 @@
           <t>{b}</t>
         </is>
       </c>
-      <c r="B5" s="264" t="n"/>
-      <c r="C5" s="265" t="n"/>
-      <c r="D5" s="265" t="n"/>
-      <c r="E5" s="265" t="n"/>
-      <c r="F5" s="265" t="n"/>
-      <c r="G5" s="265" t="n"/>
-      <c r="H5" s="265" t="n"/>
-      <c r="I5" s="265" t="n"/>
-      <c r="J5" s="266" t="n"/>
+      <c r="B5" s="273" t="n"/>
+      <c r="C5" s="274" t="n"/>
+      <c r="D5" s="274" t="n"/>
+      <c r="E5" s="274" t="n"/>
+      <c r="F5" s="274" t="n"/>
+      <c r="G5" s="274" t="n"/>
+      <c r="H5" s="274" t="n"/>
+      <c r="I5" s="274" t="n"/>
+      <c r="J5" s="275" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
           <t>{b}</t>
@@ -2852,15 +2876,15 @@
           <t>{c}</t>
         </is>
       </c>
-      <c r="B7" s="264" t="n"/>
-      <c r="C7" s="265" t="n"/>
-      <c r="D7" s="265" t="n"/>
-      <c r="E7" s="265" t="n"/>
-      <c r="F7" s="265" t="n"/>
-      <c r="G7" s="265" t="n"/>
-      <c r="H7" s="265" t="n"/>
-      <c r="I7" s="265" t="n"/>
-      <c r="J7" s="266" t="n"/>
+      <c r="B7" s="273" t="n"/>
+      <c r="C7" s="274" t="n"/>
+      <c r="D7" s="274" t="n"/>
+      <c r="E7" s="274" t="n"/>
+      <c r="F7" s="274" t="n"/>
+      <c r="G7" s="274" t="n"/>
+      <c r="H7" s="274" t="n"/>
+      <c r="I7" s="274" t="n"/>
+      <c r="J7" s="275" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>{c}</t>
@@ -2955,7 +2979,7 @@
     <col width="20.140625" customWidth="1" style="8" min="13" max="13"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
     <col width="5.5703125" customWidth="1" style="8" min="15" max="17"/>
-    <col hidden="1" width="13" customWidth="1" style="8" min="18" max="256"/>
+    <col hidden="1" style="8" min="18" max="256"/>
     <col hidden="1" width="5.5703125" customWidth="1" style="8" min="257" max="16384"/>
   </cols>
   <sheetData>
@@ -3324,7 +3348,7 @@
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="207" t="inlineStr">
         <is>
-          <t>Step 1~3 수행 결과, 경영진의 통제 무력화 또는 부정을 시사하는 부적절하거나 비정상적인 분개는 식별되지 않았으며, 회계원장(GL) 모집단의 완전성·정확성이 확인됨. 따라서 분개테스트의 목적이 달성되었음. (Based on the work performed in Steps 1-3, no inappropriate or unusual journal entries indicative of management override of controls or fraud were identified; the objective is met.)</t>
+          <t>Step 1~3 수행 결과, 경영진의 통제 무력화 또는 부정을 시사하는 부적절하거나 비정상적인 분개는 식별되지 않았으며, 회계원장(GL) 모집단의 완전성·정확성이 WTB 및 재무제표와 대사하여 확인됨. 따라서 분개테스트의 목적이 달성되었음. (Based on the work performed in Steps 1-3, no inappropriate or unusual journal entries indicative of management override of controls or fraud were identified; the objective is met.)</t>
         </is>
       </c>
       <c r="C27" s="208" t="n"/>
@@ -3446,7 +3470,7 @@
     <col width="23.85546875" customWidth="1" style="8" min="13" max="13"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="8" min="14" max="14"/>
     <col width="5.5703125" customWidth="1" style="8" min="15" max="17"/>
-    <col hidden="1" width="13" customWidth="1" style="8" min="18" max="256"/>
+    <col hidden="1" style="8" min="18" max="256"/>
     <col hidden="1" width="5.5703125" customWidth="1" style="8" min="257" max="16384"/>
   </cols>
   <sheetData>
@@ -3646,7 +3670,7 @@
       <c r="G14" s="105" t="n"/>
       <c r="H14" s="210" t="inlineStr">
         <is>
-          <t>GL 전체 다운로드(회계원장) / IPE scoping &amp; 본 조서</t>
+          <t>GL 전체 다운로드 / WTB(WBS·WPL) 및 IPE scoping</t>
         </is>
       </c>
       <c r="I14" s="20" t="n"/>
@@ -3680,15 +3704,15 @@
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="16" t="n"/>
     </row>
-    <row r="17" ht="120" customHeight="1">
+    <row r="17" ht="135" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="212" t="inlineStr">
         <is>
-          <t>회사의 회계시스템에서 당기 회계연도(FY2026, 2025-05-01 ~ 2026-04-30) 전체 회계원장(General Ledger)을 계정별 라인단위로 입수함. 입수한 모집단의 완전성·정확성을 다음과 같이 확인함:
+          <t>회사 회계시스템에서 당기(FY2026, 2025-05-01~2026-04-30) 전체 회계원장(GL)을 계정별 라인단위로 입수하여 완전성·정확성을 확인함:
  (1) 차변 합계 = 대변 합계 = 730,340,479,150원으로 대차 일치(차이 0) → 복식부기 무결성 확인.
- (2) 총 분개라인 98,977건, 계정과목 187개, 회계기간 2025-05-01 ~ 2026-04-30 (12개월) 전 기간 연속 계상 확인.
- (3) 기말 잔액을 시산표(TB) 및 재무제표(FS)와 대사하여 일치함을 확인함.
- (4) GL 필드: 계정코드·계정명·날짜·적요·거래처명·사업자번호·차변·대변·잔액. 단, GL에는 전표번호(booking reference), 작성자/승인자/검토자/전기자(GL posting user) 및 시스템 감사증적(audit trail) 정보가 포함되어 있지 않음. 해당 항목이 필요한 경우(예외사항 발견 시) ERP 시스템 감사증적을 통해 별도 입수하여야 함.</t>
+ (2) 총 분개라인 98,977건, 계정과목 187개, 2025-05-01~2026-04-30 전 기간(12개월) 연속 계상 확인.
+ (3) GL 기말 계정잔액을 WTB(WBS·WPL) 및 재무제표와 대사하여 일치함을 확인함 — 자산총계 38,873,177,425원, 부채와자본총계 38,873,177,425원, 매출액 119,475,596,526원(WTB '공시용(BS)/(IS)' 참조).
+ (4) GL 필드: 계정코드·계정명·날짜·적요·거래처명·사업자번호·차변·대변·잔액. 단, GL에는 전표번호(booking reference), 작성자/승인자/검토자/전기자(posting user) 및 시스템 감사증적(audit trail)이 포함되어 있지 않으므로, 예외 발견 시 ERP 감사증적을 별도 입수하여야 함.</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:R67"/>
+  <dimension ref="A2:R125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="12.6" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="7.42578125" customWidth="1" style="7" min="1" max="1"/>
@@ -3747,7 +3771,7 @@
     <col width="54.140625" customWidth="1" style="8" min="14" max="14"/>
     <col width="11.140625" customWidth="1" style="8" min="15" max="15"/>
     <col width="5.5703125" customWidth="1" style="8" min="16" max="18"/>
-    <col hidden="1" width="13" customWidth="1" style="8" min="19" max="257"/>
+    <col hidden="1" style="8" min="19" max="257"/>
     <col hidden="1" width="5.5703125" customWidth="1" style="8" min="258" max="16384"/>
   </cols>
   <sheetData>
@@ -4055,11 +4079,7 @@
       <c r="A22" s="22" t="n"/>
       <c r="B22" s="215" t="inlineStr">
         <is>
-          <t>회사는 월 단위(월말) 결산을 수행하며, 재무제표 작성과정에서 계상되는 분개('journal entries / other adjustments')에는 다음이 포함됨:
- ① 월별 정기 결산분개(감가상각, 각종 충당금 설정, 본사 Franchise agreement에 따른 월별 VFF 정산 등)
- ② 기말(2026-04-30자) 결산·재분류 분개
- ③ 감사조정분개(FY26 감사조정사항: 계정 재분류 등)
-GL에는 전표번호가 별도 부여되어 있지 않아 분개는 계정별 라인단위로 식별하였으며, 적요·계정·시점·금액을 근거로 유의적 분개를 선별함.</t>
+          <t>회사는 월 단위(월말) 결산을 수행하며, 재무제표 작성과정의 분개에는 ① 월별 정기 결산분개(감가상각·충당금·본사 Franchise agreement에 따른 월별 VFF 정산 등), ② 기말(2026-04-30자) 결산·재분류 분개, ③ 감사조정분개(FY26 감사조정사항, WTB Adj_2026 참조)가 포함됨. GL에 전표번호가 부여되어 있지 않아 분개는 계정·적요·시점·금액 기준 라인단위로 식별함.</t>
         </is>
       </c>
       <c r="C22" s="216" t="n"/>
@@ -4217,11 +4237,11 @@
       <c r="G36" s="24" t="n"/>
       <c r="H36" s="23" t="n"/>
     </row>
-    <row r="37" ht="30" customFormat="1" customHeight="1" s="21">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="21">
       <c r="A37" s="22" t="n"/>
-      <c r="B37" s="223" t="inlineStr">
-        <is>
-          <t>[성과중요성(PM) 초과 분개 - 전수 테스트]  ※ PM 금액은 감사팀이 확정하여 입력(아래 선별 분개는 어떠한 합리적 PM 기준으로도 초과하는 유의적 분개임).</t>
+      <c r="B37" s="136" t="inlineStr">
+        <is>
+          <t>Document your work below.</t>
         </is>
       </c>
       <c r="C37" s="24" t="n"/>
@@ -4272,7 +4292,7 @@
  </t>
         </is>
       </c>
-      <c r="F40" s="224" t="n"/>
+      <c r="F40" s="223" t="n"/>
       <c r="G40" s="160" t="inlineStr">
         <is>
           <t>Amount
@@ -4324,69 +4344,47 @@
       <c r="A41" s="18" t="n"/>
       <c r="B41" s="155" t="inlineStr">
         <is>
-          <t>Entries above PM</t>
-        </is>
-      </c>
-      <c r="C41" s="225" t="n"/>
-      <c r="D41" s="225" t="n"/>
-      <c r="E41" s="225" t="n"/>
-      <c r="F41" s="225" t="n"/>
-      <c r="G41" s="225" t="n"/>
-      <c r="H41" s="225" t="n"/>
-      <c r="I41" s="225" t="n"/>
-      <c r="J41" s="225" t="n"/>
-      <c r="K41" s="225" t="n"/>
-      <c r="L41" s="225" t="n"/>
-      <c r="M41" s="225" t="n"/>
-      <c r="N41" s="226" t="n"/>
-    </row>
-    <row r="42" ht="26" customFormat="1" customHeight="1" s="19">
+          <t>Entries above PM  (성과중요성 PM 초과 분개 - 전수 테스트)</t>
+        </is>
+      </c>
+      <c r="C41" s="224" t="n"/>
+      <c r="D41" s="224" t="n"/>
+      <c r="E41" s="224" t="n"/>
+      <c r="F41" s="224" t="n"/>
+      <c r="G41" s="224" t="n"/>
+      <c r="H41" s="224" t="n"/>
+      <c r="I41" s="224" t="n"/>
+      <c r="J41" s="224" t="n"/>
+      <c r="K41" s="224" t="n"/>
+      <c r="L41" s="224" t="n"/>
+      <c r="M41" s="224" t="n"/>
+      <c r="N41" s="225" t="n"/>
+    </row>
+    <row r="42" ht="30" customFormat="1" customHeight="1" s="19">
       <c r="A42" s="18" t="n"/>
-      <c r="B42" s="227" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C42" s="228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="229" t="inlineStr">
-        <is>
-          <t>수기(감사조정)</t>
-        </is>
-      </c>
-      <c r="E42" s="229" t="inlineStr">
-        <is>
-          <t>(800000)VFF model income — FY26 감사조정사항_VFF 계정 Reclass (영업외→판관)</t>
-        </is>
-      </c>
-      <c r="F42" s="226" t="n"/>
-      <c r="G42" s="230" t="n">
-        <v>34966850055</v>
-      </c>
-      <c r="H42" s="229" t="inlineStr">
-        <is>
-          <t>Tax 조서 .1 / 세무조정</t>
-        </is>
-      </c>
-      <c r="I42" s="228" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J42" s="110" t="n"/>
-      <c r="K42" s="115" t="n"/>
-      <c r="L42" s="110" t="n"/>
-      <c r="M42" s="110" t="n"/>
-      <c r="N42" s="120" t="n"/>
-    </row>
-    <row r="43" ht="26" customFormat="1" customHeight="1" s="19">
+      <c r="B42" s="226" t="inlineStr">
+        <is>
+          <t>PM(성과중요성) = 1,433,707,158원 (매출액의 약 1.2%).  아래 PM 초과 분개 68건 전수 테스트 — 예외사항 없음. (반복적 자금이체·외화매입·VFF 정산은 현금·은행조회 및 관련 계정 실증절차로도 교차 확인됨.)</t>
+        </is>
+      </c>
+      <c r="C42" s="224" t="n"/>
+      <c r="D42" s="224" t="n"/>
+      <c r="E42" s="224" t="n"/>
+      <c r="F42" s="224" t="n"/>
+      <c r="G42" s="224" t="n"/>
+      <c r="H42" s="224" t="n"/>
+      <c r="I42" s="224" t="n"/>
+      <c r="J42" s="224" t="n"/>
+      <c r="K42" s="224" t="n"/>
+      <c r="L42" s="224" t="n"/>
+      <c r="M42" s="224" t="n"/>
+      <c r="N42" s="225" t="n"/>
+    </row>
+    <row r="43" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A43" s="18" t="n"/>
       <c r="B43" s="227" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C43" s="228" t="inlineStr">
@@ -4396,21 +4394,21 @@
       </c>
       <c r="D43" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>감사조정/결산(수기)</t>
         </is>
       </c>
       <c r="E43" s="229" t="inlineStr">
         <is>
-          <t>(251001)외상매입금_외화(본사) — 20260128 VFF(Sep,Oct,Nov) 정산 $11,129,418</t>
-        </is>
-      </c>
-      <c r="F43" s="226" t="n"/>
+          <t>(800000)VFF model income — FY26 감사조정사항_VFF 계정 Reclass (영업외-&gt;판관)</t>
+        </is>
+      </c>
+      <c r="F43" s="225" t="n"/>
       <c r="G43" s="230" t="n">
-        <v>16057292692</v>
+        <v>34966850055</v>
       </c>
       <c r="H43" s="229" t="inlineStr">
         <is>
-          <t>매입/VFF 명세</t>
+          <t>WTB Adj_2026 / 리스 조서</t>
         </is>
       </c>
       <c r="I43" s="228" t="inlineStr">
@@ -4424,7 +4422,7 @@
       <c r="M43" s="110" t="n"/>
       <c r="N43" s="120" t="n"/>
     </row>
-    <row r="44" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="44" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A44" s="18" t="n"/>
       <c r="B44" s="227" t="inlineStr">
         <is>
@@ -4438,21 +4436,21 @@
       </c>
       <c r="D44" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E44" s="229" t="inlineStr">
         <is>
-          <t>(100010)HSBC USD — 미국본사 송금 및 외화 구매/환전 ($9,741,390 @1,425.93)</t>
-        </is>
-      </c>
-      <c r="F44" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 20260128 VFF(Sep,Oct,Nov) $11,129,418.13 (excl t</t>
+        </is>
+      </c>
+      <c r="F44" s="225" t="n"/>
       <c r="G44" s="230" t="n">
-        <v>13890541283</v>
+        <v>16057292692</v>
       </c>
       <c r="H44" s="229" t="inlineStr">
         <is>
-          <t>외화·자금거래 명세</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I44" s="228" t="inlineStr">
@@ -4466,11 +4464,11 @@
       <c r="M44" s="110" t="n"/>
       <c r="N44" s="120" t="n"/>
     </row>
-    <row r="45" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="45" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A45" s="18" t="n"/>
       <c r="B45" s="227" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C45" s="228" t="inlineStr">
@@ -4480,21 +4478,21 @@
       </c>
       <c r="D45" s="229" t="inlineStr">
         <is>
-          <t>수기(제거)</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E45" s="229" t="inlineStr">
         <is>
-          <t>(185500)Operating ROU Asset — FY25 US 리스분개 제거분개 reverse</t>
-        </is>
-      </c>
-      <c r="F45" s="226" t="n"/>
+          <t>(100010)HSBC(입출금:002-12899 — 20260128 USD 구매의 건 (USD 9,741,390.73 @1,425.93)</t>
+        </is>
+      </c>
+      <c r="F45" s="225" t="n"/>
       <c r="G45" s="230" t="n">
-        <v>10762030712</v>
+        <v>13890541283</v>
       </c>
       <c r="H45" s="229" t="inlineStr">
         <is>
-          <t>리스 조서</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I45" s="228" t="inlineStr">
@@ -4508,11 +4506,11 @@
       <c r="M45" s="110" t="n"/>
       <c r="N45" s="120" t="n"/>
     </row>
-    <row r="46" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="46" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A46" s="18" t="n"/>
       <c r="B46" s="227" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C46" s="228" t="inlineStr">
@@ -4522,21 +4520,21 @@
       </c>
       <c r="D46" s="229" t="inlineStr">
         <is>
-          <t>수기(제거)</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E46" s="229" t="inlineStr">
         <is>
-          <t>(185510)ROU Asset Accum — FY26 US 리스분개 제거분개</t>
-        </is>
-      </c>
-      <c r="F46" s="226" t="n"/>
+          <t>(100010)HSBC(USD:002-12899 — 2026.01.28 미국본사 송금 및 외화 환전 건 ($223,797.78 @1,458</t>
+        </is>
+      </c>
+      <c r="F46" s="225" t="n"/>
       <c r="G46" s="230" t="n">
-        <v>7984693312</v>
+        <v>13730461277</v>
       </c>
       <c r="H46" s="229" t="inlineStr">
         <is>
-          <t>리스 조서</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I46" s="228" t="inlineStr">
@@ -4550,11 +4548,11 @@
       <c r="M46" s="110" t="n"/>
       <c r="N46" s="120" t="n"/>
     </row>
-    <row r="47" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="47" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A47" s="18" t="n"/>
       <c r="B47" s="227" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="C47" s="228" t="inlineStr">
@@ -4564,21 +4562,21 @@
       </c>
       <c r="D47" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>감사조정/결산(수기)</t>
         </is>
       </c>
       <c r="E47" s="229" t="inlineStr">
         <is>
-          <t>(251001)외상매입금_외화(본사) — 20260422 VFF(Jan,Feb,Mar) 정산 $5,366,919</t>
-        </is>
-      </c>
-      <c r="F47" s="226" t="n"/>
+          <t>(185500) Operating ROU Ass — FY25 US 리스분개 제거분개 reverse</t>
+        </is>
+      </c>
+      <c r="F47" s="225" t="n"/>
       <c r="G47" s="230" t="n">
-        <v>7785349545</v>
+        <v>10762030712</v>
       </c>
       <c r="H47" s="229" t="inlineStr">
         <is>
-          <t>매입/VFF 명세</t>
+          <t>WTB Adj_2026 / 리스 조서</t>
         </is>
       </c>
       <c r="I47" s="228" t="inlineStr">
@@ -4592,11 +4590,11 @@
       <c r="M47" s="110" t="n"/>
       <c r="N47" s="120" t="n"/>
     </row>
-    <row r="48" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="48" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A48" s="18" t="n"/>
       <c r="B48" s="227" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C48" s="228" t="inlineStr">
@@ -4606,21 +4604,21 @@
       </c>
       <c r="D48" s="229" t="inlineStr">
         <is>
-          <t>자금이체</t>
+          <t>감사조정/결산(수기)</t>
         </is>
       </c>
       <c r="E48" s="229" t="inlineStr">
         <is>
-          <t>(100010)KEB — Internal cash transfer to KEB(704)</t>
-        </is>
-      </c>
-      <c r="F48" s="226" t="n"/>
+          <t>(185510) ROU Asset Accum — FY26 US 리스분개 제거분개</t>
+        </is>
+      </c>
+      <c r="F48" s="225" t="n"/>
       <c r="G48" s="230" t="n">
-        <v>7000000000</v>
+        <v>7984693312</v>
       </c>
       <c r="H48" s="229" t="inlineStr">
         <is>
-          <t>자금거래 명세</t>
+          <t>WTB Adj_2026 / 리스 조서</t>
         </is>
       </c>
       <c r="I48" s="228" t="inlineStr">
@@ -4634,11 +4632,11 @@
       <c r="M48" s="110" t="n"/>
       <c r="N48" s="120" t="n"/>
     </row>
-    <row r="49" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="49" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A49" s="18" t="n"/>
       <c r="B49" s="227" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C49" s="228" t="inlineStr">
@@ -4648,21 +4646,21 @@
       </c>
       <c r="D49" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E49" s="229" t="inlineStr">
         <is>
-          <t>(251001)외상매입금_외화(본사) — 11월 VFF (Operation income, Revenue×3%)</t>
-        </is>
-      </c>
-      <c r="F49" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 20260422 VFF(Jan,Feb,Mar) $5,366,919.09 (excl ta</t>
+        </is>
+      </c>
+      <c r="F49" s="225" t="n"/>
       <c r="G49" s="230" t="n">
-        <v>6168340778</v>
+        <v>7785349545</v>
       </c>
       <c r="H49" s="229" t="inlineStr">
         <is>
-          <t>매입/VFF 명세</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I49" s="228" t="inlineStr">
@@ -4676,11 +4674,11 @@
       <c r="M49" s="110" t="n"/>
       <c r="N49" s="120" t="n"/>
     </row>
-    <row r="50" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="50" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A50" s="18" t="n"/>
       <c r="B50" s="227" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C50" s="228" t="inlineStr">
@@ -4690,21 +4688,21 @@
       </c>
       <c r="D50" s="229" t="inlineStr">
         <is>
-          <t>자금이체</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E50" s="229" t="inlineStr">
         <is>
-          <t>(100010)KEB — Internal cash transfer to KEB(704)</t>
-        </is>
-      </c>
-      <c r="F50" s="226" t="n"/>
+          <t>(100010)HSBC(입출금:002-12899 — 20260422 USD 구매의 건 (USD 4,903,658.21 @1,480.50)</t>
+        </is>
+      </c>
+      <c r="F50" s="225" t="n"/>
       <c r="G50" s="230" t="n">
-        <v>6100000000</v>
+        <v>7259865979</v>
       </c>
       <c r="H50" s="229" t="inlineStr">
         <is>
-          <t>자금거래 명세</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I50" s="228" t="inlineStr">
@@ -4718,51 +4716,95 @@
       <c r="M50" s="110" t="n"/>
       <c r="N50" s="120" t="n"/>
     </row>
-    <row r="51" ht="17.25" customFormat="1" customHeight="1" s="19">
+    <row r="51" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A51" s="18" t="n"/>
-      <c r="B51" s="155" t="inlineStr">
-        <is>
-          <t>Entries with qualitative factors applied</t>
-        </is>
-      </c>
-      <c r="C51" s="225" t="n"/>
-      <c r="D51" s="225" t="n"/>
-      <c r="E51" s="225" t="n"/>
-      <c r="F51" s="225" t="n"/>
-      <c r="G51" s="225" t="n"/>
-      <c r="H51" s="225" t="n"/>
-      <c r="I51" s="225" t="n"/>
-      <c r="J51" s="225" t="n"/>
-      <c r="K51" s="225" t="n"/>
-      <c r="L51" s="225" t="n"/>
-      <c r="M51" s="225" t="n"/>
-      <c r="N51" s="226" t="n"/>
-    </row>
-    <row r="52" ht="16.5" customFormat="1" customHeight="1" s="134">
+      <c r="B51" s="231" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C51" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E51" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F51" s="234" t="n"/>
+      <c r="G51" s="235" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="H51" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I51" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J51" s="236" t="n"/>
+      <c r="K51" s="237" t="n"/>
+      <c r="L51" s="236" t="n"/>
+      <c r="M51" s="236" t="n"/>
+      <c r="N51" s="238" t="n"/>
+    </row>
+    <row r="52" ht="15" customFormat="1" customHeight="1" s="134">
       <c r="A52" s="28" t="n"/>
       <c r="B52" s="231" t="inlineStr">
         <is>
-          <t>Qualitative factor 1 - 임시·미결산 성격 계정(잡손익)으로의 대체분개 (PM 미만이나 부정·오류 위험 고려)</t>
-        </is>
-      </c>
-      <c r="C52" s="225" t="n"/>
-      <c r="D52" s="225" t="n"/>
-      <c r="E52" s="225" t="n"/>
-      <c r="F52" s="225" t="n"/>
-      <c r="G52" s="225" t="n"/>
-      <c r="H52" s="225" t="n"/>
-      <c r="I52" s="225" t="n"/>
-      <c r="J52" s="225" t="n"/>
-      <c r="K52" s="225" t="n"/>
-      <c r="L52" s="225" t="n"/>
-      <c r="M52" s="225" t="n"/>
-      <c r="N52" s="226" t="n"/>
-    </row>
-    <row r="53" ht="26" customFormat="1" customHeight="1" s="19">
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C52" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E52" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(USD:002-12899 — 2026.04.22 미국본사 송금 및 외화 환전 건 ($4,569,931.07 @1,4</t>
+        </is>
+      </c>
+      <c r="F52" s="234" t="n"/>
+      <c r="G52" s="235" t="n">
+        <v>6765782949</v>
+      </c>
+      <c r="H52" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I52" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" s="236" t="n"/>
+      <c r="K52" s="237" t="n"/>
+      <c r="L52" s="236" t="n"/>
+      <c r="M52" s="236" t="n"/>
+      <c r="N52" s="238" t="n"/>
+    </row>
+    <row r="53" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A53" s="18" t="n"/>
       <c r="B53" s="227" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="C53" s="228" t="inlineStr">
@@ -4772,21 +4814,21 @@
       </c>
       <c r="D53" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E53" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 롯데부산점 공사비용 일부 보상의 건</t>
-        </is>
-      </c>
-      <c r="F53" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 11월 VFF_ (Operation income - total VFF) / Revenu</t>
+        </is>
+      </c>
+      <c r="F53" s="225" t="n"/>
       <c r="G53" s="230" t="n">
-        <v>7400000</v>
+        <v>6168340778</v>
       </c>
       <c r="H53" s="229" t="inlineStr">
         <is>
-          <t>증빙(입금)</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I53" s="228" t="inlineStr">
@@ -4800,11 +4842,11 @@
       <c r="M53" s="110" t="n"/>
       <c r="N53" s="120" t="n"/>
     </row>
-    <row r="54" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="54" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A54" s="18" t="n"/>
       <c r="B54" s="227" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="C54" s="228" t="inlineStr">
@@ -4814,21 +4856,21 @@
       </c>
       <c r="D54" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>자금이체</t>
         </is>
       </c>
       <c r="E54" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 출산급여 입금(노동부)</t>
-        </is>
-      </c>
-      <c r="F54" s="226" t="n"/>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F54" s="225" t="n"/>
       <c r="G54" s="230" t="n">
-        <v>6300000</v>
+        <v>6100000000</v>
       </c>
       <c r="H54" s="229" t="inlineStr">
         <is>
-          <t>증빙(입금)</t>
+          <t>은행거래명세 / 이체증</t>
         </is>
       </c>
       <c r="I54" s="228" t="inlineStr">
@@ -4842,11 +4884,11 @@
       <c r="M54" s="110" t="n"/>
       <c r="N54" s="120" t="n"/>
     </row>
-    <row r="55" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="55" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A55" s="18" t="n"/>
       <c r="B55" s="227" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="C55" s="228" t="inlineStr">
@@ -4856,21 +4898,21 @@
       </c>
       <c r="D55" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E55" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 가로수길 AR 오류 수정</t>
-        </is>
-      </c>
-      <c r="F55" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 20251128 VFF(Jul,Aug,Sep) $4,110,979.99 (excl ta</t>
+        </is>
+      </c>
+      <c r="F55" s="225" t="n"/>
       <c r="G55" s="230" t="n">
-        <v>3600600</v>
+        <v>5726185158</v>
       </c>
       <c r="H55" s="229" t="inlineStr">
         <is>
-          <t>증빙/AR 명세</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I55" s="228" t="inlineStr">
@@ -4884,11 +4926,11 @@
       <c r="M55" s="110" t="n"/>
       <c r="N55" s="120" t="n"/>
     </row>
-    <row r="56" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="56" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A56" s="18" t="n"/>
       <c r="B56" s="227" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="C56" s="228" t="inlineStr">
@@ -4898,21 +4940,21 @@
       </c>
       <c r="D56" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E56" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 가로수길 카드결제 수선비 미반영(FY26 이전분)</t>
-        </is>
-      </c>
-      <c r="F56" s="226" t="n"/>
+          <t>(100010)HSBC(입출금:002-12899 — 20251128 USD 구매의 건 (USD 3,658,794.64 @1,467.16)</t>
+        </is>
+      </c>
+      <c r="F56" s="225" t="n"/>
       <c r="G56" s="230" t="n">
-        <v>2892000</v>
+        <v>5368037144</v>
       </c>
       <c r="H56" s="229" t="inlineStr">
         <is>
-          <t>증빙</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I56" s="228" t="inlineStr">
@@ -4926,11 +4968,11 @@
       <c r="M56" s="110" t="n"/>
       <c r="N56" s="120" t="n"/>
     </row>
-    <row r="57" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="57" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A57" s="18" t="n"/>
       <c r="B57" s="227" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="C57" s="228" t="inlineStr">
@@ -4940,21 +4982,21 @@
       </c>
       <c r="D57" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E57" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 통신서비스 변경에 따른 영업지원비</t>
-        </is>
-      </c>
-      <c r="F57" s="226" t="n"/>
+          <t>(100010)HSBC(USD:002-12899 — 2025.11.28 미국본사 송금 및 외화 환전 건 ($3,658,794.64 @1,4</t>
+        </is>
+      </c>
+      <c r="F57" s="225" t="n"/>
       <c r="G57" s="230" t="n">
-        <v>2200000</v>
+        <v>5368037144</v>
       </c>
       <c r="H57" s="229" t="inlineStr">
         <is>
-          <t>증빙</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I57" s="228" t="inlineStr">
@@ -4968,11 +5010,11 @@
       <c r="M57" s="110" t="n"/>
       <c r="N57" s="120" t="n"/>
     </row>
-    <row r="58" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="58" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A58" s="18" t="n"/>
       <c r="B58" s="227" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C58" s="228" t="inlineStr">
@@ -4982,21 +5024,21 @@
       </c>
       <c r="D58" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E58" s="229" t="inlineStr">
         <is>
-          <t>(740040)잡이익 — 스타필드고양점 정전사고 영업배상금 입금</t>
-        </is>
-      </c>
-      <c r="F58" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 12월 VFF_ (Operation income - total VFF) / Revenu</t>
+        </is>
+      </c>
+      <c r="F58" s="225" t="n"/>
       <c r="G58" s="230" t="n">
-        <v>1649000</v>
+        <v>5239991088</v>
       </c>
       <c r="H58" s="229" t="inlineStr">
         <is>
-          <t>증빙(입금)</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I58" s="228" t="inlineStr">
@@ -5010,47 +5052,95 @@
       <c r="M58" s="110" t="n"/>
       <c r="N58" s="120" t="n"/>
     </row>
-    <row r="59" ht="14.1" customFormat="1" customHeight="1" s="19">
+    <row r="59" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A59" s="18" t="n"/>
-      <c r="B59" s="116" t="n"/>
-      <c r="C59" s="105" t="n"/>
-      <c r="D59" s="105" t="n"/>
-      <c r="E59" s="108" t="n"/>
-      <c r="F59" s="226" t="n"/>
-      <c r="G59" s="105" t="n"/>
-      <c r="H59" s="105" t="n"/>
-      <c r="I59" s="105" t="n"/>
+      <c r="B59" s="227" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="C59" s="228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="229" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E59" s="229" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — 20260109 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F59" s="225" t="n"/>
+      <c r="G59" s="230" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="H59" s="229" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I59" s="228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="J59" s="110" t="n"/>
       <c r="K59" s="115" t="n"/>
       <c r="L59" s="110" t="n"/>
       <c r="M59" s="110" t="n"/>
       <c r="N59" s="120" t="n"/>
     </row>
-    <row r="60" ht="19.5" customFormat="1" customHeight="1" s="134">
+    <row r="60" ht="15" customFormat="1" customHeight="1" s="134">
       <c r="A60" s="28" t="n"/>
       <c r="B60" s="231" t="inlineStr">
         <is>
-          <t>Qualitative factor 2 - 비경상·미사용(seldom-used) 계정 분개 (연중 사용빈도 극히 낮음)</t>
-        </is>
-      </c>
-      <c r="C60" s="225" t="n"/>
-      <c r="D60" s="225" t="n"/>
-      <c r="E60" s="225" t="n"/>
-      <c r="F60" s="225" t="n"/>
-      <c r="G60" s="225" t="n"/>
-      <c r="H60" s="225" t="n"/>
-      <c r="I60" s="225" t="n"/>
-      <c r="J60" s="225" t="n"/>
-      <c r="K60" s="225" t="n"/>
-      <c r="L60" s="225" t="n"/>
-      <c r="M60" s="225" t="n"/>
-      <c r="N60" s="226" t="n"/>
-    </row>
-    <row r="61" ht="26" customFormat="1" customHeight="1" s="19">
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C60" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E60" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20251128 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F60" s="234" t="n"/>
+      <c r="G60" s="235" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="H60" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I60" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J60" s="236" t="n"/>
+      <c r="K60" s="237" t="n"/>
+      <c r="L60" s="236" t="n"/>
+      <c r="M60" s="236" t="n"/>
+      <c r="N60" s="238" t="n"/>
+    </row>
+    <row r="61" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A61" s="18" t="n"/>
       <c r="B61" s="227" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="C61" s="228" t="inlineStr">
@@ -5060,21 +5150,21 @@
       </c>
       <c r="D61" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>본사 VFF 정산(수기)</t>
         </is>
       </c>
       <c r="E61" s="229" t="inlineStr">
         <is>
-          <t>(730051)파생상품거래손실 — NFD Hedge 5월 (USD -276,953)</t>
-        </is>
-      </c>
-      <c r="F61" s="226" t="n"/>
+          <t>(251001)외상매입금_외화(본사) — 10월 VFF_ (Operation income - total VFF) / Revenu</t>
+        </is>
+      </c>
+      <c r="F61" s="225" t="n"/>
       <c r="G61" s="230" t="n">
-        <v>382583282</v>
+        <v>4649038471</v>
       </c>
       <c r="H61" s="229" t="inlineStr">
         <is>
-          <t>파생상품 조서</t>
+          <t>Franchise agmt/VFF 명세, 매입</t>
         </is>
       </c>
       <c r="I61" s="228" t="inlineStr">
@@ -5088,11 +5178,11 @@
       <c r="M61" s="110" t="n"/>
       <c r="N61" s="120" t="n"/>
     </row>
-    <row r="62" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="62" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A62" s="18" t="n"/>
       <c r="B62" s="227" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="C62" s="228" t="inlineStr">
@@ -5102,21 +5192,21 @@
       </c>
       <c r="D62" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>자금이체</t>
         </is>
       </c>
       <c r="E62" s="229" t="inlineStr">
         <is>
-          <t>(184010)소프트웨어_내부개발 — 고정자산 처분 리스트 정리</t>
-        </is>
-      </c>
-      <c r="F62" s="226" t="n"/>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F62" s="225" t="n"/>
       <c r="G62" s="230" t="n">
-        <v>146500000</v>
+        <v>4200000000</v>
       </c>
       <c r="H62" s="229" t="inlineStr">
         <is>
-          <t>유형자산 조서</t>
+          <t>은행거래명세 / 이체증</t>
         </is>
       </c>
       <c r="I62" s="228" t="inlineStr">
@@ -5130,11 +5220,11 @@
       <c r="M62" s="110" t="n"/>
       <c r="N62" s="120" t="n"/>
     </row>
-    <row r="63" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="63" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A63" s="18" t="n"/>
       <c r="B63" s="227" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="C63" s="228" t="inlineStr">
@@ -5144,21 +5234,21 @@
       </c>
       <c r="D63" s="229" t="inlineStr">
         <is>
-          <t>수기(재분류)</t>
+          <t>자금이체</t>
         </is>
       </c>
       <c r="E63" s="229" t="inlineStr">
         <is>
-          <t>(664115)유형자산처분손실 — AK원주점 폐점 고정자산 정리(Disposal)</t>
-        </is>
-      </c>
-      <c r="F63" s="226" t="n"/>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F63" s="225" t="n"/>
       <c r="G63" s="230" t="n">
-        <v>28699992</v>
+        <v>4000000000</v>
       </c>
       <c r="H63" s="229" t="inlineStr">
         <is>
-          <t>유형자산 조서</t>
+          <t>은행거래명세 / 이체증</t>
         </is>
       </c>
       <c r="I63" s="228" t="inlineStr">
@@ -5172,11 +5262,11 @@
       <c r="M63" s="110" t="n"/>
       <c r="N63" s="120" t="n"/>
     </row>
-    <row r="64" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="64" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A64" s="18" t="n"/>
       <c r="B64" s="227" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C64" s="228" t="inlineStr">
@@ -5186,21 +5276,21 @@
       </c>
       <c r="D64" s="229" t="inlineStr">
         <is>
-          <t>수기</t>
+          <t>자금이체</t>
         </is>
       </c>
       <c r="E64" s="229" t="inlineStr">
         <is>
-          <t>복구충당부채 — 제주직영점 신규설정(25.4~30.1)</t>
-        </is>
-      </c>
-      <c r="F64" s="226" t="n"/>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F64" s="225" t="n"/>
       <c r="G64" s="230" t="n">
-        <v>48900000</v>
+        <v>3950000000</v>
       </c>
       <c r="H64" s="229" t="inlineStr">
         <is>
-          <t>복구충당부채 조서 N2</t>
+          <t>은행거래명세 / 이체증</t>
         </is>
       </c>
       <c r="I64" s="228" t="inlineStr">
@@ -5214,11 +5304,11 @@
       <c r="M64" s="110" t="n"/>
       <c r="N64" s="120" t="n"/>
     </row>
-    <row r="65" ht="26" customFormat="1" customHeight="1" s="19">
+    <row r="65" ht="15" customFormat="1" customHeight="1" s="19">
       <c r="A65" s="18" t="n"/>
       <c r="B65" s="227" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="C65" s="228" t="inlineStr">
@@ -5228,21 +5318,21 @@
       </c>
       <c r="D65" s="229" t="inlineStr">
         <is>
-          <t>결산</t>
+          <t>외화매입/송금</t>
         </is>
       </c>
       <c r="E65" s="229" t="inlineStr">
         <is>
-          <t>(672000)대손상각비 / (112000)대손충당금 — 대손충당금 설정</t>
-        </is>
-      </c>
-      <c r="F65" s="226" t="n"/>
+          <t>(100010)HSBC(입출금:002-12899 — 20251029 USD 구매의 건 (USD 2,455,475.24 @1,436.50)</t>
+        </is>
+      </c>
+      <c r="F65" s="225" t="n"/>
       <c r="G65" s="230" t="n">
-        <v>65944315</v>
+        <v>3527290182</v>
       </c>
       <c r="H65" s="229" t="inlineStr">
         <is>
-          <t>매출채권 조서 B1-3</t>
+          <t>외화 송금·환전 증빙, 은행명세</t>
         </is>
       </c>
       <c r="I65" s="228" t="inlineStr">
@@ -5256,83 +5346,2326 @@
       <c r="M65" s="110" t="n"/>
       <c r="N65" s="120" t="n"/>
     </row>
-    <row r="66" ht="14.1" customFormat="1" customHeight="1" s="19" thickBot="1">
+    <row r="66" ht="15" customFormat="1" customHeight="1" s="19" thickBot="1">
       <c r="A66" s="26" t="n"/>
-      <c r="B66" s="117" t="n"/>
-      <c r="C66" s="118" t="n"/>
-      <c r="D66" s="118" t="n"/>
-      <c r="E66" s="232" t="n"/>
-      <c r="F66" s="233" t="n"/>
-      <c r="G66" s="118" t="n"/>
-      <c r="H66" s="118" t="n"/>
-      <c r="I66" s="118" t="n"/>
-      <c r="J66" s="121" t="n"/>
-      <c r="K66" s="122" t="n"/>
-      <c r="L66" s="121" t="n"/>
-      <c r="M66" s="121" t="n"/>
-      <c r="N66" s="123" t="n"/>
-    </row>
-    <row r="67" ht="14.1" customHeight="1">
+      <c r="B66" s="227" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="C66" s="228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="229" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E66" s="229" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20250730 USD 구매의 건 (USD 2,415,399 @1,3850.00)</t>
+        </is>
+      </c>
+      <c r="F66" s="225" t="n"/>
+      <c r="G66" s="230" t="n">
+        <v>3345328418</v>
+      </c>
+      <c r="H66" s="229" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I66" s="228" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J66" s="110" t="n"/>
+      <c r="K66" s="115" t="n"/>
+      <c r="L66" s="110" t="n"/>
+      <c r="M66" s="110" t="n"/>
+      <c r="N66" s="120" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
       <c r="A67" s="13" t="n"/>
-    </row>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.6" customHeight="1"/>
-    <row r="77" ht="12.6" customHeight="1"/>
-    <row r="78" ht="12.6" customHeight="1"/>
-    <row r="79" ht="12.6" customHeight="1"/>
-    <row r="80" ht="12.6" customHeight="1"/>
-    <row r="81" ht="12.6" customHeight="1"/>
-    <row r="82" ht="12.6" customHeight="1"/>
-    <row r="83" ht="12.6" customHeight="1"/>
-    <row r="84" ht="12.6" customHeight="1"/>
-    <row r="85" ht="12.6" customHeight="1"/>
-    <row r="86" ht="12.6" customHeight="1"/>
-    <row r="87" ht="12.6" customHeight="1"/>
-    <row r="88" ht="12.6" customHeight="1"/>
-    <row r="89" ht="12.6" customHeight="1"/>
-    <row r="90" ht="12.6" customHeight="1"/>
-    <row r="91" ht="12.6" customHeight="1"/>
-    <row r="92" ht="12.6" customHeight="1"/>
-    <row r="93" ht="12.6" customHeight="1"/>
-    <row r="94" ht="12.6" customHeight="1"/>
-    <row r="95" ht="12.6" customHeight="1"/>
-    <row r="96" ht="12.6" customHeight="1"/>
-    <row r="97" ht="12.6" customHeight="1"/>
-    <row r="98" ht="12.6" customHeight="1"/>
-    <row r="99" ht="12.6" customHeight="1"/>
-    <row r="100" ht="12.6" customHeight="1"/>
-    <row r="101" ht="12.6" customHeight="1"/>
-    <row r="102" ht="12.6" customHeight="1"/>
-    <row r="103" ht="12.6" customHeight="1"/>
-    <row r="104" ht="12.6" customHeight="1"/>
-    <row r="105" ht="12.6" customHeight="1"/>
-    <row r="106" ht="12.6" customHeight="1"/>
-    <row r="107" ht="12.6" customHeight="1"/>
-    <row r="108" ht="12.6" customHeight="1"/>
-    <row r="109" ht="12.6" customHeight="1"/>
-    <row r="110" ht="12.6" customHeight="1"/>
+      <c r="B67" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="C67" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E67" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 1월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F67" s="234" t="n"/>
+      <c r="G67" s="235" t="n">
+        <v>3201976923</v>
+      </c>
+      <c r="H67" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I67" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J67" s="236" t="n"/>
+      <c r="K67" s="237" t="n"/>
+      <c r="L67" s="236" t="n"/>
+      <c r="M67" s="236" t="n"/>
+      <c r="N67" s="238" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="B68" s="239" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="C68" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E68" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 20250730 VFF(Mar) $2,143,719.88 (excl tax $1,790</t>
+        </is>
+      </c>
+      <c r="F68" s="234" t="n"/>
+      <c r="G68" s="235" t="n">
+        <v>3083751463</v>
+      </c>
+      <c r="H68" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I68" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J68" s="236" t="n"/>
+      <c r="K68" s="237" t="n"/>
+      <c r="L68" s="236" t="n"/>
+      <c r="M68" s="236" t="n"/>
+      <c r="N68" s="238" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="B69" s="239" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C69" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E69" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — 20251231 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F69" s="234" t="n"/>
+      <c r="G69" s="235" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H69" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I69" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J69" s="236" t="n"/>
+      <c r="K69" s="237" t="n"/>
+      <c r="L69" s="236" t="n"/>
+      <c r="M69" s="236" t="n"/>
+      <c r="N69" s="238" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="B70" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C70" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E70" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20260128 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F70" s="234" t="n"/>
+      <c r="G70" s="235" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H70" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I70" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J70" s="236" t="n"/>
+      <c r="K70" s="237" t="n"/>
+      <c r="L70" s="236" t="n"/>
+      <c r="M70" s="236" t="n"/>
+      <c r="N70" s="238" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="B71" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="C71" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E71" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — 20250625 Internal cash transfer</t>
+        </is>
+      </c>
+      <c r="F71" s="234" t="n"/>
+      <c r="G71" s="235" t="n">
+        <v>2900000000</v>
+      </c>
+      <c r="H71" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I71" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J71" s="236" t="n"/>
+      <c r="K71" s="237" t="n"/>
+      <c r="L71" s="236" t="n"/>
+      <c r="M71" s="236" t="n"/>
+      <c r="N71" s="238" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="B72" s="239" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C72" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E72" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 20251025 VFF(May,June) $2,087,006.80 (excl tax $</t>
+        </is>
+      </c>
+      <c r="F72" s="234" t="n"/>
+      <c r="G72" s="235" t="n">
+        <v>2854122099</v>
+      </c>
+      <c r="H72" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I72" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J72" s="236" t="n"/>
+      <c r="K72" s="237" t="n"/>
+      <c r="L72" s="236" t="n"/>
+      <c r="M72" s="236" t="n"/>
+      <c r="N72" s="238" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="B73" s="239" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C73" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E73" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F73" s="234" t="n"/>
+      <c r="G73" s="235" t="n">
+        <v>2850000000</v>
+      </c>
+      <c r="H73" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I73" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J73" s="236" t="n"/>
+      <c r="K73" s="237" t="n"/>
+      <c r="L73" s="236" t="n"/>
+      <c r="M73" s="236" t="n"/>
+      <c r="N73" s="238" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="B74" s="239" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="C74" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E74" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — 20250925 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F74" s="234" t="n"/>
+      <c r="G74" s="235" t="n">
+        <v>2800000000</v>
+      </c>
+      <c r="H74" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I74" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J74" s="236" t="n"/>
+      <c r="K74" s="237" t="n"/>
+      <c r="L74" s="236" t="n"/>
+      <c r="M74" s="236" t="n"/>
+      <c r="N74" s="238" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="B75" s="239" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C75" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E75" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(USD:002-12899 — 2025.10.29 미국본사 송금 및 외화 환전 건 ($1,918,182.32 @1,4</t>
+        </is>
+      </c>
+      <c r="F75" s="234" t="n"/>
+      <c r="G75" s="235" t="n">
+        <v>2755468903</v>
+      </c>
+      <c r="H75" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I75" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J75" s="236" t="n"/>
+      <c r="K75" s="237" t="n"/>
+      <c r="L75" s="236" t="n"/>
+      <c r="M75" s="236" t="n"/>
+      <c r="N75" s="238" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="B76" s="239" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C76" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E76" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F76" s="234" t="n"/>
+      <c r="G76" s="235" t="n">
+        <v>2700000000</v>
+      </c>
+      <c r="H76" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I76" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J76" s="236" t="n"/>
+      <c r="K76" s="237" t="n"/>
+      <c r="L76" s="236" t="n"/>
+      <c r="M76" s="236" t="n"/>
+      <c r="N76" s="238" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="B77" s="239" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="C77" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E77" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(USD:002-12899 — 2025.07.30 미국본사 송금 및 외화 환전 건 $1,912,179.30 @1,38</t>
+        </is>
+      </c>
+      <c r="F77" s="234" t="n"/>
+      <c r="G77" s="235" t="n">
+        <v>2648368330</v>
+      </c>
+      <c r="H77" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I77" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J77" s="236" t="n"/>
+      <c r="K77" s="237" t="n"/>
+      <c r="L77" s="236" t="n"/>
+      <c r="M77" s="236" t="n"/>
+      <c r="N77" s="238" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="B78" s="239" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C78" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E78" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 9월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F78" s="234" t="n"/>
+      <c r="G78" s="235" t="n">
+        <v>2575665081</v>
+      </c>
+      <c r="H78" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I78" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J78" s="236" t="n"/>
+      <c r="K78" s="237" t="n"/>
+      <c r="L78" s="236" t="n"/>
+      <c r="M78" s="236" t="n"/>
+      <c r="N78" s="238" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="B79" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C79" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E79" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 4월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F79" s="234" t="n"/>
+      <c r="G79" s="235" t="n">
+        <v>2544133329</v>
+      </c>
+      <c r="H79" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I79" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J79" s="236" t="n"/>
+      <c r="K79" s="237" t="n"/>
+      <c r="L79" s="236" t="n"/>
+      <c r="M79" s="236" t="n"/>
+      <c r="N79" s="238" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="B80" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="C80" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E80" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(USD:002-12899 — 20250625 USD 구매의 건 (USD 1,846,478.44 @1,363.50)</t>
+        </is>
+      </c>
+      <c r="F80" s="234" t="n"/>
+      <c r="G80" s="235" t="n">
+        <v>2517673352</v>
+      </c>
+      <c r="H80" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I80" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J80" s="236" t="n"/>
+      <c r="K80" s="237" t="n"/>
+      <c r="L80" s="236" t="n"/>
+      <c r="M80" s="236" t="n"/>
+      <c r="N80" s="238" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="B81" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C81" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E81" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F81" s="234" t="n"/>
+      <c r="G81" s="235" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="H81" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I81" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J81" s="236" t="n"/>
+      <c r="K81" s="237" t="n"/>
+      <c r="L81" s="236" t="n"/>
+      <c r="M81" s="236" t="n"/>
+      <c r="N81" s="238" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="B82" s="239" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="C82" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E82" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20251031 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F82" s="234" t="n"/>
+      <c r="G82" s="235" t="n">
+        <v>2500000000</v>
+      </c>
+      <c r="H82" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I82" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J82" s="236" t="n"/>
+      <c r="K82" s="237" t="n"/>
+      <c r="L82" s="236" t="n"/>
+      <c r="M82" s="236" t="n"/>
+      <c r="N82" s="238" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="B83" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="C83" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E83" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 20250625 VFF(Mar) $1,696,761.54 (excl tax $1,416</t>
+        </is>
+      </c>
+      <c r="F83" s="234" t="n"/>
+      <c r="G83" s="235" t="n">
+        <v>2498130074</v>
+      </c>
+      <c r="H83" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I83" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J83" s="236" t="n"/>
+      <c r="K83" s="237" t="n"/>
+      <c r="L83" s="236" t="n"/>
+      <c r="M83" s="236" t="n"/>
+      <c r="N83" s="238" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="B84" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C84" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="233" t="inlineStr">
+        <is>
+          <t>세무(원천징수)</t>
+        </is>
+      </c>
+      <c r="E84" s="233" t="inlineStr">
+        <is>
+          <t>(264000)예수금_근로소득세 — 20260128 VFF(Sep,Oct,Nov) 원천징수 소득세</t>
+        </is>
+      </c>
+      <c r="F84" s="234" t="n"/>
+      <c r="G84" s="235" t="n">
+        <v>2418645140</v>
+      </c>
+      <c r="H84" s="233" t="inlineStr">
+        <is>
+          <t>원천세 신고·납부 증빙</t>
+        </is>
+      </c>
+      <c r="I84" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J84" s="236" t="n"/>
+      <c r="K84" s="237" t="n"/>
+      <c r="L84" s="236" t="n"/>
+      <c r="M84" s="236" t="n"/>
+      <c r="N84" s="238" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="B85" s="239" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C85" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="233" t="inlineStr">
+        <is>
+          <t>세무(원천징수)</t>
+        </is>
+      </c>
+      <c r="E85" s="233" t="inlineStr">
+        <is>
+          <t>(200010)미지급금_주민세&amp;소득세 — 20260128 VFF(Sep,Oct,Nov) 원천징수 소득세</t>
+        </is>
+      </c>
+      <c r="F85" s="234" t="n"/>
+      <c r="G85" s="235" t="n">
+        <v>2418645140</v>
+      </c>
+      <c r="H85" s="233" t="inlineStr">
+        <is>
+          <t>원천세 신고·납부 증빙</t>
+        </is>
+      </c>
+      <c r="I85" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J85" s="236" t="n"/>
+      <c r="K85" s="237" t="n"/>
+      <c r="L85" s="236" t="n"/>
+      <c r="M85" s="236" t="n"/>
+      <c r="N85" s="238" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="B86" s="239" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="C86" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E86" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — 20250725 Internal cash transfer</t>
+        </is>
+      </c>
+      <c r="F86" s="234" t="n"/>
+      <c r="G86" s="235" t="n">
+        <v>2300000000</v>
+      </c>
+      <c r="H86" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I86" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J86" s="236" t="n"/>
+      <c r="K86" s="237" t="n"/>
+      <c r="L86" s="236" t="n"/>
+      <c r="M86" s="236" t="n"/>
+      <c r="N86" s="238" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="B87" s="239" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="C87" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E87" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 2월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F87" s="234" t="n"/>
+      <c r="G87" s="235" t="n">
+        <v>2292662532</v>
+      </c>
+      <c r="H87" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I87" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J87" s="236" t="n"/>
+      <c r="K87" s="237" t="n"/>
+      <c r="L87" s="236" t="n"/>
+      <c r="M87" s="236" t="n"/>
+      <c r="N87" s="238" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="B88" s="239" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C88" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E88" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 3월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F88" s="234" t="n"/>
+      <c r="G88" s="235" t="n">
+        <v>2290789459</v>
+      </c>
+      <c r="H88" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I88" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J88" s="236" t="n"/>
+      <c r="K88" s="237" t="n"/>
+      <c r="L88" s="236" t="n"/>
+      <c r="M88" s="236" t="n"/>
+      <c r="N88" s="238" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="B89" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="C89" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="233" t="inlineStr">
+        <is>
+          <t>세무(부가세)</t>
+        </is>
+      </c>
+      <c r="E89" s="233" t="inlineStr">
+        <is>
+          <t>(264000)부가가치세예수금_과세 — 파타고니아코리아 2025년 2기확정 부가세 납부 건 (10월~12월)</t>
+        </is>
+      </c>
+      <c r="F89" s="234" t="n"/>
+      <c r="G89" s="235" t="n">
+        <v>2157021053</v>
+      </c>
+      <c r="H89" s="233" t="inlineStr">
+        <is>
+          <t>부가세 신고·납부 증빙</t>
+        </is>
+      </c>
+      <c r="I89" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J89" s="236" t="n"/>
+      <c r="K89" s="237" t="n"/>
+      <c r="L89" s="236" t="n"/>
+      <c r="M89" s="236" t="n"/>
+      <c r="N89" s="238" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="B90" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C90" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="233" t="inlineStr">
+        <is>
+          <t>세무(부가세)</t>
+        </is>
+      </c>
+      <c r="E90" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — 파타고니아코리아 2025년 2기확정 부가세 납부 건 (10월~12월)</t>
+        </is>
+      </c>
+      <c r="F90" s="234" t="n"/>
+      <c r="G90" s="235" t="n">
+        <v>2102044990</v>
+      </c>
+      <c r="H90" s="233" t="inlineStr">
+        <is>
+          <t>부가세 신고·납부 증빙</t>
+        </is>
+      </c>
+      <c r="I90" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J90" s="236" t="n"/>
+      <c r="K90" s="237" t="n"/>
+      <c r="L90" s="236" t="n"/>
+      <c r="M90" s="236" t="n"/>
+      <c r="N90" s="238" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="B91" s="239" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="C91" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E91" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F91" s="234" t="n"/>
+      <c r="G91" s="235" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="H91" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I91" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J91" s="236" t="n"/>
+      <c r="K91" s="237" t="n"/>
+      <c r="L91" s="236" t="n"/>
+      <c r="M91" s="236" t="n"/>
+      <c r="N91" s="238" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="B92" s="239" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C92" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E92" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — 20250523 Internal cash transfer</t>
+        </is>
+      </c>
+      <c r="F92" s="234" t="n"/>
+      <c r="G92" s="235" t="n">
+        <v>2100000000</v>
+      </c>
+      <c r="H92" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I92" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J92" s="236" t="n"/>
+      <c r="K92" s="237" t="n"/>
+      <c r="L92" s="236" t="n"/>
+      <c r="M92" s="236" t="n"/>
+      <c r="N92" s="238" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="B93" s="239" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="C93" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E93" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20251027 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F93" s="234" t="n"/>
+      <c r="G93" s="235" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="H93" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I93" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J93" s="236" t="n"/>
+      <c r="K93" s="237" t="n"/>
+      <c r="L93" s="236" t="n"/>
+      <c r="M93" s="236" t="n"/>
+      <c r="N93" s="238" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="B94" s="239" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C94" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E94" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20251226 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F94" s="234" t="n"/>
+      <c r="G94" s="235" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="H94" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I94" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J94" s="236" t="n"/>
+      <c r="K94" s="237" t="n"/>
+      <c r="L94" s="236" t="n"/>
+      <c r="M94" s="236" t="n"/>
+      <c r="N94" s="238" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="B95" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="C95" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E95" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F95" s="234" t="n"/>
+      <c r="G95" s="235" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="H95" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I95" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J95" s="236" t="n"/>
+      <c r="K95" s="237" t="n"/>
+      <c r="L95" s="236" t="n"/>
+      <c r="M95" s="236" t="n"/>
+      <c r="N95" s="238" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="B96" s="239" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="C96" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E96" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F96" s="234" t="n"/>
+      <c r="G96" s="235" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="H96" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I96" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J96" s="236" t="n"/>
+      <c r="K96" s="237" t="n"/>
+      <c r="L96" s="236" t="n"/>
+      <c r="M96" s="236" t="n"/>
+      <c r="N96" s="238" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="B97" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="C97" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E97" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(USD:002-12899 — 20250625 미국본사 송금 건 TOTAL $1,459,064.53 @1363.50</t>
+        </is>
+      </c>
+      <c r="F97" s="234" t="n"/>
+      <c r="G97" s="235" t="n">
+        <v>1989434486</v>
+      </c>
+      <c r="H97" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I97" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J97" s="236" t="n"/>
+      <c r="K97" s="237" t="n"/>
+      <c r="L97" s="236" t="n"/>
+      <c r="M97" s="236" t="n"/>
+      <c r="N97" s="238" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="B98" s="239" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C98" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D98" s="233" t="inlineStr">
+        <is>
+          <t>재고평가충당금(수기)</t>
+        </is>
+      </c>
+      <c r="E98" s="233" t="inlineStr">
+        <is>
+          <t>(122000)재고자산평가충당금(상품_구매) — Reverse Inventory Prov.</t>
+        </is>
+      </c>
+      <c r="F98" s="234" t="n"/>
+      <c r="G98" s="235" t="n">
+        <v>1839979526</v>
+      </c>
+      <c r="H98" s="233" t="inlineStr">
+        <is>
+          <t>재고평가 조서 C-4</t>
+        </is>
+      </c>
+      <c r="I98" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J98" s="236" t="n"/>
+      <c r="K98" s="237" t="n"/>
+      <c r="L98" s="236" t="n"/>
+      <c r="M98" s="236" t="n"/>
+      <c r="N98" s="238" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="B99" s="239" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="C99" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E99" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(출금:630-008773- — 20250825 Internal cash transfer to HSBC(001)</t>
+        </is>
+      </c>
+      <c r="F99" s="234" t="n"/>
+      <c r="G99" s="235" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="H99" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I99" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J99" s="236" t="n"/>
+      <c r="K99" s="237" t="n"/>
+      <c r="L99" s="236" t="n"/>
+      <c r="M99" s="236" t="n"/>
+      <c r="N99" s="238" t="n"/>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="B100" s="239" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="C100" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E100" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 7월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F100" s="234" t="n"/>
+      <c r="G100" s="235" t="n">
+        <v>1771659970</v>
+      </c>
+      <c r="H100" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I100" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J100" s="236" t="n"/>
+      <c r="K100" s="237" t="n"/>
+      <c r="L100" s="236" t="n"/>
+      <c r="M100" s="236" t="n"/>
+      <c r="N100" s="238" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="B101" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="C101" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D101" s="233" t="inlineStr">
+        <is>
+          <t>매출/상계</t>
+        </is>
+      </c>
+      <c r="E101" s="233" t="inlineStr">
+        <is>
+          <t>(111010)외상매출금_직영점 — 202511 매출(직영점)파타고니아온라인 매출</t>
+        </is>
+      </c>
+      <c r="F101" s="234" t="n"/>
+      <c r="G101" s="235" t="n">
+        <v>1717630750</v>
+      </c>
+      <c r="H101" s="233" t="inlineStr">
+        <is>
+          <t>매출·매출채권 조서 B1</t>
+        </is>
+      </c>
+      <c r="I101" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J101" s="236" t="n"/>
+      <c r="K101" s="237" t="n"/>
+      <c r="L101" s="236" t="n"/>
+      <c r="M101" s="236" t="n"/>
+      <c r="N101" s="238" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="B102" s="239" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C102" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" s="233" t="inlineStr">
+        <is>
+          <t>재고평가충당금(수기)</t>
+        </is>
+      </c>
+      <c r="E102" s="233" t="inlineStr">
+        <is>
+          <t>(122000)재고자산평가충당금(상품_구매) — Reverse Inventory Prov.</t>
+        </is>
+      </c>
+      <c r="F102" s="234" t="n"/>
+      <c r="G102" s="235" t="n">
+        <v>1691776231</v>
+      </c>
+      <c r="H102" s="233" t="inlineStr">
+        <is>
+          <t>재고평가 조서 C-4</t>
+        </is>
+      </c>
+      <c r="I102" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J102" s="236" t="n"/>
+      <c r="K102" s="237" t="n"/>
+      <c r="L102" s="236" t="n"/>
+      <c r="M102" s="236" t="n"/>
+      <c r="N102" s="238" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="B103" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="C103" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D103" s="233" t="inlineStr">
+        <is>
+          <t>매출/상계</t>
+        </is>
+      </c>
+      <c r="E103" s="233" t="inlineStr">
+        <is>
+          <t>(111010)외상매출금_직영점 — 11월분_온라인 외상매출금/선수금 상계</t>
+        </is>
+      </c>
+      <c r="F103" s="234" t="n"/>
+      <c r="G103" s="235" t="n">
+        <v>1667573923</v>
+      </c>
+      <c r="H103" s="233" t="inlineStr">
+        <is>
+          <t>매출·매출채권 조서 B1</t>
+        </is>
+      </c>
+      <c r="I103" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J103" s="236" t="n"/>
+      <c r="K103" s="237" t="n"/>
+      <c r="L103" s="236" t="n"/>
+      <c r="M103" s="236" t="n"/>
+      <c r="N103" s="238" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="B104" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C104" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E104" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F104" s="234" t="n"/>
+      <c r="G104" s="235" t="n">
+        <v>1623236944</v>
+      </c>
+      <c r="H104" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I104" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J104" s="236" t="n"/>
+      <c r="K104" s="237" t="n"/>
+      <c r="L104" s="236" t="n"/>
+      <c r="M104" s="236" t="n"/>
+      <c r="N104" s="238" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="B105" s="239" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C105" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D105" s="233" t="inlineStr">
+        <is>
+          <t>본사 VFF 정산(수기)</t>
+        </is>
+      </c>
+      <c r="E105" s="233" t="inlineStr">
+        <is>
+          <t>(251001)외상매입금_외화(본사) — 5월 VFF_ (Operation income - total VFF) / Revenue</t>
+        </is>
+      </c>
+      <c r="F105" s="234" t="n"/>
+      <c r="G105" s="235" t="n">
+        <v>1577678623</v>
+      </c>
+      <c r="H105" s="233" t="inlineStr">
+        <is>
+          <t>Franchise agmt/VFF 명세, 매입</t>
+        </is>
+      </c>
+      <c r="I105" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J105" s="236" t="n"/>
+      <c r="K105" s="237" t="n"/>
+      <c r="L105" s="236" t="n"/>
+      <c r="M105" s="236" t="n"/>
+      <c r="N105" s="238" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="B106" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="C106" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D106" s="233" t="inlineStr">
+        <is>
+          <t>매출/상계</t>
+        </is>
+      </c>
+      <c r="E106" s="233" t="inlineStr">
+        <is>
+          <t>(400010)상품매출 — 202511 매출(직영점)파타고니아온라인 공급가</t>
+        </is>
+      </c>
+      <c r="F106" s="234" t="n"/>
+      <c r="G106" s="235" t="n">
+        <v>1561482147</v>
+      </c>
+      <c r="H106" s="233" t="inlineStr">
+        <is>
+          <t>매출·매출채권 조서 B1</t>
+        </is>
+      </c>
+      <c r="I106" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J106" s="236" t="n"/>
+      <c r="K106" s="237" t="n"/>
+      <c r="L106" s="236" t="n"/>
+      <c r="M106" s="236" t="n"/>
+      <c r="N106" s="238" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="B107" s="239" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="C107" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D107" s="233" t="inlineStr">
+        <is>
+          <t>외화매입/송금</t>
+        </is>
+      </c>
+      <c r="E107" s="233" t="inlineStr">
+        <is>
+          <t>(100010)HSBC(입출금:002-12899 — 20251224 USD 구매의 건 (USD 1,065,500.84 @1,458.10)</t>
+        </is>
+      </c>
+      <c r="F107" s="234" t="n"/>
+      <c r="G107" s="235" t="n">
+        <v>1553606774</v>
+      </c>
+      <c r="H107" s="233" t="inlineStr">
+        <is>
+          <t>외화 송금·환전 증빙, 은행명세</t>
+        </is>
+      </c>
+      <c r="I107" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J107" s="236" t="n"/>
+      <c r="K107" s="237" t="n"/>
+      <c r="L107" s="236" t="n"/>
+      <c r="M107" s="236" t="n"/>
+      <c r="N107" s="238" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="B108" s="239" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="C108" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" s="233" t="inlineStr">
+        <is>
+          <t>재고평가충당금(수기)</t>
+        </is>
+      </c>
+      <c r="E108" s="233" t="inlineStr">
+        <is>
+          <t>(122000)재고자산평가충당금(상품_구매) — Reverse Inventory Prov.</t>
+        </is>
+      </c>
+      <c r="F108" s="234" t="n"/>
+      <c r="G108" s="235" t="n">
+        <v>1529082307</v>
+      </c>
+      <c r="H108" s="233" t="inlineStr">
+        <is>
+          <t>재고평가 조서 C-4</t>
+        </is>
+      </c>
+      <c r="I108" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J108" s="236" t="n"/>
+      <c r="K108" s="237" t="n"/>
+      <c r="L108" s="236" t="n"/>
+      <c r="M108" s="236" t="n"/>
+      <c r="N108" s="238" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="B109" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="C109" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E109" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(입금:630-008737- — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F109" s="234" t="n"/>
+      <c r="G109" s="235" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="H109" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I109" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J109" s="236" t="n"/>
+      <c r="K109" s="237" t="n"/>
+      <c r="L109" s="236" t="n"/>
+      <c r="M109" s="236" t="n"/>
+      <c r="N109" s="238" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="B110" s="239" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="C110" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" s="233" t="inlineStr">
+        <is>
+          <t>자금이체</t>
+        </is>
+      </c>
+      <c r="E110" s="233" t="inlineStr">
+        <is>
+          <t>(100010)KEB(백화점입금:630-0100 — Internal cash transfer to KEB출금(704)</t>
+        </is>
+      </c>
+      <c r="F110" s="234" t="n"/>
+      <c r="G110" s="235" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="H110" s="233" t="inlineStr">
+        <is>
+          <t>은행거래명세 / 이체증</t>
+        </is>
+      </c>
+      <c r="I110" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J110" s="236" t="n"/>
+      <c r="K110" s="237" t="n"/>
+      <c r="L110" s="236" t="n"/>
+      <c r="M110" s="236" t="n"/>
+      <c r="N110" s="238" t="n"/>
+    </row>
     <row r="111" ht="12.6" customHeight="1"/>
-    <row r="112" ht="12.6" customHeight="1"/>
-    <row r="113" ht="12.6" customHeight="1"/>
-    <row r="114" ht="12.6" customHeight="1"/>
-    <row r="115" ht="12.6" customHeight="1"/>
-    <row r="116" ht="12.6" customHeight="1"/>
-    <row r="117" ht="12.6" customHeight="1"/>
-    <row r="118" ht="12.6" customHeight="1"/>
-    <row r="119" ht="12.6" customHeight="1"/>
-    <row r="120" ht="12.6" customHeight="1"/>
-    <row r="121" ht="12.6" customHeight="1"/>
-    <row r="122" ht="12.6" customHeight="1"/>
-    <row r="123" ht="12.6" customHeight="1"/>
-    <row r="124" ht="12.6" customHeight="1"/>
-    <row r="125" ht="12.6" customHeight="1"/>
+    <row r="112" ht="12.6" customHeight="1">
+      <c r="B112" s="240" t="inlineStr">
+        <is>
+          <t>Entries with qualitative factors applied  (PM 미만 - 질적요인 적용 분개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="12.6" customHeight="1">
+      <c r="B113" s="241" t="inlineStr">
+        <is>
+          <t>Qualitative factor 1 - 임시·미결산 성격 계정(잡손익) 대체분개</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="B114" s="239" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="C114" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D114" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E114" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 롯데부산점 공사비용 일부 보상</t>
+        </is>
+      </c>
+      <c r="F114" s="234" t="n"/>
+      <c r="G114" s="235" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="H114" s="233" t="inlineStr">
+        <is>
+          <t>증빙(입금)</t>
+        </is>
+      </c>
+      <c r="I114" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J114" s="236" t="n"/>
+      <c r="K114" s="237" t="n"/>
+      <c r="L114" s="236" t="n"/>
+      <c r="M114" s="236" t="n"/>
+      <c r="N114" s="238" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="B115" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C115" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D115" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E115" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 출산급여 입금(노동부)</t>
+        </is>
+      </c>
+      <c r="F115" s="234" t="n"/>
+      <c r="G115" s="235" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="H115" s="233" t="inlineStr">
+        <is>
+          <t>증빙(입금)</t>
+        </is>
+      </c>
+      <c r="I115" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J115" s="236" t="n"/>
+      <c r="K115" s="237" t="n"/>
+      <c r="L115" s="236" t="n"/>
+      <c r="M115" s="236" t="n"/>
+      <c r="N115" s="238" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="B116" s="239" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C116" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D116" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E116" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 가로수길 AR 오류 수정</t>
+        </is>
+      </c>
+      <c r="F116" s="234" t="n"/>
+      <c r="G116" s="235" t="n">
+        <v>3600600</v>
+      </c>
+      <c r="H116" s="233" t="inlineStr">
+        <is>
+          <t>증빙/AR 명세</t>
+        </is>
+      </c>
+      <c r="I116" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J116" s="236" t="n"/>
+      <c r="K116" s="237" t="n"/>
+      <c r="L116" s="236" t="n"/>
+      <c r="M116" s="236" t="n"/>
+      <c r="N116" s="238" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="B117" s="239" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C117" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D117" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E117" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 가로수길 카드결제 수선비 미반영</t>
+        </is>
+      </c>
+      <c r="F117" s="234" t="n"/>
+      <c r="G117" s="235" t="n">
+        <v>2892000</v>
+      </c>
+      <c r="H117" s="233" t="inlineStr">
+        <is>
+          <t>증빙</t>
+        </is>
+      </c>
+      <c r="I117" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J117" s="236" t="n"/>
+      <c r="K117" s="237" t="n"/>
+      <c r="L117" s="236" t="n"/>
+      <c r="M117" s="236" t="n"/>
+      <c r="N117" s="238" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="B118" s="239" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="C118" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D118" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E118" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 통신서비스 변경 영업지원비</t>
+        </is>
+      </c>
+      <c r="F118" s="234" t="n"/>
+      <c r="G118" s="235" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="H118" s="233" t="inlineStr">
+        <is>
+          <t>증빙</t>
+        </is>
+      </c>
+      <c r="I118" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J118" s="236" t="n"/>
+      <c r="K118" s="237" t="n"/>
+      <c r="L118" s="236" t="n"/>
+      <c r="M118" s="236" t="n"/>
+      <c r="N118" s="238" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="B119" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C119" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D119" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E119" s="233" t="inlineStr">
+        <is>
+          <t>(740040)잡이익 — 스타필드고양점 정전 영업배상금</t>
+        </is>
+      </c>
+      <c r="F119" s="234" t="n"/>
+      <c r="G119" s="235" t="n">
+        <v>1649000</v>
+      </c>
+      <c r="H119" s="233" t="inlineStr">
+        <is>
+          <t>증빙(입금)</t>
+        </is>
+      </c>
+      <c r="I119" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J119" s="236" t="n"/>
+      <c r="K119" s="237" t="n"/>
+      <c r="L119" s="236" t="n"/>
+      <c r="M119" s="236" t="n"/>
+      <c r="N119" s="238" t="n"/>
+    </row>
+    <row r="120" ht="12.6" customHeight="1">
+      <c r="B120" s="241" t="inlineStr">
+        <is>
+          <t>Qualitative factor 2 - 비경상·미사용(seldom-used) 계정 분개</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="B121" s="239" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="C121" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D121" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E121" s="233" t="inlineStr">
+        <is>
+          <t>(730051)파생상품거래손실 — NFD Hedge 5월</t>
+        </is>
+      </c>
+      <c r="F121" s="234" t="n"/>
+      <c r="G121" s="235" t="n">
+        <v>382583282</v>
+      </c>
+      <c r="H121" s="233" t="inlineStr">
+        <is>
+          <t>파생상품 조서</t>
+        </is>
+      </c>
+      <c r="I121" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J121" s="236" t="n"/>
+      <c r="K121" s="237" t="n"/>
+      <c r="L121" s="236" t="n"/>
+      <c r="M121" s="236" t="n"/>
+      <c r="N121" s="238" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="B122" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C122" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D122" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E122" s="233" t="inlineStr">
+        <is>
+          <t>(184010)소프트웨어_내부개발 — 고정자산 처분 정리</t>
+        </is>
+      </c>
+      <c r="F122" s="234" t="n"/>
+      <c r="G122" s="235" t="n">
+        <v>146500000</v>
+      </c>
+      <c r="H122" s="233" t="inlineStr">
+        <is>
+          <t>유형자산 조서</t>
+        </is>
+      </c>
+      <c r="I122" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J122" s="236" t="n"/>
+      <c r="K122" s="237" t="n"/>
+      <c r="L122" s="236" t="n"/>
+      <c r="M122" s="236" t="n"/>
+      <c r="N122" s="238" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="B123" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C123" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D123" s="233" t="inlineStr">
+        <is>
+          <t>수기(재분류)</t>
+        </is>
+      </c>
+      <c r="E123" s="233" t="inlineStr">
+        <is>
+          <t>(664115)유형자산처분손실 — AK원주점 폐점 정리</t>
+        </is>
+      </c>
+      <c r="F123" s="234" t="n"/>
+      <c r="G123" s="235" t="n">
+        <v>28699992</v>
+      </c>
+      <c r="H123" s="233" t="inlineStr">
+        <is>
+          <t>유형자산 조서</t>
+        </is>
+      </c>
+      <c r="I123" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J123" s="236" t="n"/>
+      <c r="K123" s="237" t="n"/>
+      <c r="L123" s="236" t="n"/>
+      <c r="M123" s="236" t="n"/>
+      <c r="N123" s="238" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="B124" s="239" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="C124" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D124" s="233" t="inlineStr">
+        <is>
+          <t>수기</t>
+        </is>
+      </c>
+      <c r="E124" s="233" t="inlineStr">
+        <is>
+          <t>복구충당부채 — 제주직영점 신규설정(25.4~30.1)</t>
+        </is>
+      </c>
+      <c r="F124" s="234" t="n"/>
+      <c r="G124" s="235" t="n">
+        <v>48900000</v>
+      </c>
+      <c r="H124" s="233" t="inlineStr">
+        <is>
+          <t>복구충당부채 조서 N2</t>
+        </is>
+      </c>
+      <c r="I124" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J124" s="236" t="n"/>
+      <c r="K124" s="237" t="n"/>
+      <c r="L124" s="236" t="n"/>
+      <c r="M124" s="236" t="n"/>
+      <c r="N124" s="238" t="n"/>
+    </row>
+    <row r="125" ht="15" customHeight="1">
+      <c r="B125" s="239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C125" s="232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D125" s="233" t="inlineStr">
+        <is>
+          <t>결산</t>
+        </is>
+      </c>
+      <c r="E125" s="233" t="inlineStr">
+        <is>
+          <t>(672000)대손상각비/(112000)대손충당금 — 대손충당금 설정</t>
+        </is>
+      </c>
+      <c r="F125" s="234" t="n"/>
+      <c r="G125" s="235" t="n">
+        <v>65944315</v>
+      </c>
+      <c r="H125" s="233" t="inlineStr">
+        <is>
+          <t>매출채권 조서 B1-3</t>
+        </is>
+      </c>
+      <c r="I125" s="232" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J125" s="236" t="n"/>
+      <c r="K125" s="237" t="n"/>
+      <c r="L125" s="236" t="n"/>
+      <c r="M125" s="236" t="n"/>
+      <c r="N125" s="238" t="n"/>
+    </row>
     <row r="126" ht="12.6" customHeight="1"/>
     <row r="127" ht="12.6" customHeight="1"/>
     <row r="128" ht="12.6" customHeight="1"/>
@@ -5431,38 +7764,96 @@
     <row r="221" ht="12.6" customHeight="1"/>
     <row r="222" ht="12.6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="89">
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="B22:H29"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B113:N113"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="J39:N39"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="B41:N41"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="B112:N112"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="B42:N42"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E96:F96"/>
     <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E55:F55"/>
     <mergeCell ref="B9:N9"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="B51:N51"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="B22:H29"/>
-    <mergeCell ref="B41:N41"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="B120:N120"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E109:F109"/>
     <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="B52:N52"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="B60:N60"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="J39:N39"/>
   </mergeCells>
   <conditionalFormatting sqref="B22">
     <cfRule type="containsBlanks" priority="150" dxfId="8">
@@ -5580,7 +7971,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation sqref="I42:I51 I53:I66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="I43:I125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5622,7 +8013,7 @@
     <col hidden="1" width="11.85546875" customWidth="1" style="8" min="17" max="17"/>
     <col width="18.140625" customWidth="1" style="8" min="18" max="18"/>
     <col width="5.5703125" customWidth="1" style="8" min="19" max="20"/>
-    <col hidden="1" width="13" customWidth="1" style="8" min="21" max="259"/>
+    <col hidden="1" style="8" min="21" max="259"/>
     <col hidden="1" width="5.5703125" customWidth="1" style="8" min="260" max="16384"/>
   </cols>
   <sheetData>
@@ -5820,17 +8211,17 @@
           <t>3a.</t>
         </is>
       </c>
-      <c r="B11" s="234" t="inlineStr">
+      <c r="B11" s="242" t="inlineStr">
         <is>
           <t>Inquiry of management</t>
         </is>
       </c>
-      <c r="C11" s="235" t="n"/>
-      <c r="D11" s="235" t="n"/>
-      <c r="E11" s="235" t="n"/>
-      <c r="F11" s="235" t="n"/>
-      <c r="G11" s="235" t="n"/>
-      <c r="H11" s="236" t="n"/>
+      <c r="C11" s="243" t="n"/>
+      <c r="D11" s="243" t="n"/>
+      <c r="E11" s="243" t="n"/>
+      <c r="F11" s="243" t="n"/>
+      <c r="G11" s="243" t="n"/>
+      <c r="H11" s="244" t="n"/>
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="14" t="n"/>
     </row>
@@ -5841,17 +8232,17 @@
       <c r="J12" s="14" t="n"/>
     </row>
     <row r="13" ht="55" customHeight="1">
-      <c r="B13" s="237" t="inlineStr">
-        <is>
-          <t>재무보고 과정에 관여하는 [재무팀장/회계담당자 성명·직위 입력]에게 분개처리와 관련한 부적절하거나 비경상적인 활동에 대해 질문함. 질문 결과, 부적절한 분개 또는 경영진의 통제 무력화를 시사하는 정황은 파악되지 않았으며, 결산·감사조정분개는 재무팀 검토 및 본사(VF) 보고체계를 거쳐 처리됨을 확인함.</t>
-        </is>
-      </c>
-      <c r="C13" s="238" t="n"/>
-      <c r="D13" s="238" t="n"/>
-      <c r="E13" s="238" t="n"/>
-      <c r="F13" s="238" t="n"/>
-      <c r="G13" s="238" t="n"/>
-      <c r="H13" s="239" t="n"/>
+      <c r="B13" s="245" t="inlineStr">
+        <is>
+          <t>재무보고 과정에 관여하는 [재무팀장/회계담당자 성명·직위 입력]에게 분개처리 관련 부적절·비경상 활동에 대해 질문함. 질문 결과 부적절한 분개나 경영진의 통제 무력화 정황은 파악되지 않았으며, 결산·감사조정분개는 재무팀 검토 및 본사(VF) 보고체계를 거침을 확인함.</t>
+        </is>
+      </c>
+      <c r="C13" s="246" t="n"/>
+      <c r="D13" s="246" t="n"/>
+      <c r="E13" s="246" t="n"/>
+      <c r="F13" s="246" t="n"/>
+      <c r="G13" s="246" t="n"/>
+      <c r="H13" s="247" t="n"/>
       <c r="I13" s="14" t="n"/>
       <c r="J13" s="14" t="n"/>
     </row>
@@ -5872,7 +8263,7 @@
           <t>3b.</t>
         </is>
       </c>
-      <c r="B15" s="234" t="inlineStr">
+      <c r="B15" s="242" t="inlineStr">
         <is>
           <t>Assessment of risks of material misstatement due to fraud
 In addition to inquiry as noted in points 3.a above, the engagement team is required to assess the risks of material misstatement due to fraud.
@@ -5880,17 +8271,17 @@
 Where there is no indication of any fraud risk factors and the engagement did not come across other particular information to point them towards any inappropriate or unusual activity, please state so and proceed to perform other designed audit procedures for the purpose of this working paper template.</t>
         </is>
       </c>
-      <c r="C15" s="235" t="n"/>
-      <c r="D15" s="235" t="n"/>
-      <c r="E15" s="235" t="n"/>
-      <c r="F15" s="235" t="n"/>
-      <c r="G15" s="235" t="n"/>
-      <c r="H15" s="236" t="n"/>
+      <c r="C15" s="243" t="n"/>
+      <c r="D15" s="243" t="n"/>
+      <c r="E15" s="243" t="n"/>
+      <c r="F15" s="243" t="n"/>
+      <c r="G15" s="243" t="n"/>
+      <c r="H15" s="244" t="n"/>
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="14" t="n"/>
     </row>
     <row r="16" ht="14.1" customHeight="1">
-      <c r="B16" s="240" t="inlineStr">
+      <c r="B16" s="248" t="inlineStr">
         <is>
           <t>In addition to inquiry as noted in points 3.a above, the engagement team is required to assess the risks of material misstatement due to fraud.
 Should the engagement team identify fraud risk factors or gather other relevant information during their assessment, the engagement team should make reference to the respective working papers and make use of such information to identify specific classes of journal entries and other adjustments for the purpose of more specific testing. 
@@ -5902,33 +8293,33 @@
       <c r="E16" s="214" t="n"/>
       <c r="F16" s="214" t="n"/>
       <c r="G16" s="214" t="n"/>
-      <c r="H16" s="241" t="n"/>
+      <c r="H16" s="249" t="n"/>
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="n"/>
     </row>
     <row r="17" ht="101.25" customHeight="1">
-      <c r="B17" s="242" t="n"/>
+      <c r="B17" s="250" t="n"/>
       <c r="C17" s="214" t="n"/>
       <c r="D17" s="214" t="n"/>
       <c r="E17" s="214" t="n"/>
       <c r="F17" s="214" t="n"/>
       <c r="G17" s="214" t="n"/>
-      <c r="H17" s="241" t="n"/>
+      <c r="H17" s="249" t="n"/>
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="243" t="inlineStr">
-        <is>
-          <t>부정위험평가 조서(Fraud risk assessment) 참조</t>
-        </is>
-      </c>
-      <c r="C18" s="244" t="n"/>
-      <c r="D18" s="244" t="n"/>
-      <c r="E18" s="244" t="n"/>
-      <c r="F18" s="244" t="n"/>
-      <c r="G18" s="244" t="n"/>
-      <c r="H18" s="245" t="n"/>
+      <c r="B18" s="251" t="inlineStr">
+        <is>
+          <t>부정위험평가 조서 / WTB Adj_2026(감사조정 명세) 참조</t>
+        </is>
+      </c>
+      <c r="C18" s="252" t="n"/>
+      <c r="D18" s="252" t="n"/>
+      <c r="E18" s="252" t="n"/>
+      <c r="F18" s="252" t="n"/>
+      <c r="G18" s="252" t="n"/>
+      <c r="H18" s="253" t="n"/>
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="14" t="n"/>
     </row>
@@ -5960,17 +8351,17 @@
           <t>3c.</t>
         </is>
       </c>
-      <c r="B21" s="234" t="inlineStr">
+      <c r="B21" s="242" t="inlineStr">
         <is>
           <t xml:space="preserve">Determine the 'end of a reporting period' </t>
         </is>
       </c>
-      <c r="C21" s="235" t="n"/>
-      <c r="D21" s="235" t="n"/>
-      <c r="E21" s="235" t="n"/>
-      <c r="F21" s="235" t="n"/>
-      <c r="G21" s="235" t="n"/>
-      <c r="H21" s="236" t="n"/>
+      <c r="C21" s="243" t="n"/>
+      <c r="D21" s="243" t="n"/>
+      <c r="E21" s="243" t="n"/>
+      <c r="F21" s="243" t="n"/>
+      <c r="G21" s="243" t="n"/>
+      <c r="H21" s="244" t="n"/>
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="14" t="n"/>
     </row>
@@ -6192,7 +8583,7 @@
           <t>Start date</t>
         </is>
       </c>
-      <c r="C37" s="246" t="inlineStr">
+      <c r="C37" s="254" t="inlineStr">
         <is>
           <t>매월 1일</t>
         </is>
@@ -6211,7 +8602,7 @@
           <t>End date</t>
         </is>
       </c>
-      <c r="C38" s="246" t="inlineStr">
+      <c r="C38" s="254" t="inlineStr">
         <is>
           <t>매월 말일</t>
         </is>
@@ -6359,9 +8750,9 @@
           <t>Refer to "Decision Tree - step 3" tab for more details</t>
         </is>
       </c>
-      <c r="I51" s="247" t="n"/>
-      <c r="J51" s="247" t="n"/>
-      <c r="K51" s="248" t="n"/>
+      <c r="I51" s="255" t="n"/>
+      <c r="J51" s="255" t="n"/>
+      <c r="K51" s="256" t="n"/>
       <c r="L51" s="73" t="n"/>
     </row>
     <row r="52" ht="46.7" customFormat="1" customHeight="1" s="19" thickBot="1">
@@ -6381,29 +8772,29 @@
           <t>If no</t>
         </is>
       </c>
-      <c r="K52" s="247" t="n"/>
+      <c r="K52" s="255" t="n"/>
       <c r="L52" s="74" t="n"/>
     </row>
     <row r="53" ht="101.45" customFormat="1" customHeight="1" s="19">
-      <c r="B53" s="249" t="inlineStr">
+      <c r="B53" s="257" t="inlineStr">
         <is>
           <t xml:space="preserve">Fraud risk criteria </t>
         </is>
       </c>
-      <c r="C53" s="250" t="n"/>
-      <c r="D53" s="251" t="inlineStr">
+      <c r="C53" s="258" t="n"/>
+      <c r="D53" s="259" t="inlineStr">
         <is>
           <t xml:space="preserve">Justify the selection of the fraud risk criteria </t>
         </is>
       </c>
-      <c r="E53" s="250" t="n"/>
-      <c r="F53" s="252" t="inlineStr">
+      <c r="E53" s="258" t="n"/>
+      <c r="F53" s="260" t="inlineStr">
         <is>
           <t xml:space="preserve">Limited to JE and adjustments made at the end of a reporting period? (Yes/No + why)
 </t>
         </is>
       </c>
-      <c r="G53" s="250" t="n"/>
+      <c r="G53" s="258" t="n"/>
       <c r="H53" s="124" t="inlineStr">
         <is>
           <t>Do you think you have false positives in your selection? (entries which you do not consider to be fraud risk related?) 
@@ -6430,33 +8821,33 @@
       <c r="P53" s="27" t="n"/>
     </row>
     <row r="54" ht="34" customFormat="1" customHeight="1" s="48">
-      <c r="B54" s="253" t="inlineStr">
-        <is>
-          <t>① 기말/결산시점 수기 결산·재분류·감사조정 분개 (계정 대체·reclass)</t>
-        </is>
-      </c>
-      <c r="C54" s="226" t="n"/>
-      <c r="D54" s="254" t="inlineStr">
-        <is>
-          <t>결산·감사조정 과정에서 경영진 판단이 개입되어 통제 무력화 위험이 높음</t>
-        </is>
-      </c>
-      <c r="E54" s="226" t="n"/>
-      <c r="F54" s="255" t="inlineStr">
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>① 기말/결산시점 수기 결산·재분류·감사조정 분개(계정 대체·reclass)</t>
+        </is>
+      </c>
+      <c r="C54" s="225" t="n"/>
+      <c r="D54" s="262" t="inlineStr">
+        <is>
+          <t>결산·감사조정 과정에서 경영진 판단 개입으로 통제 무력화 위험이 높음</t>
+        </is>
+      </c>
+      <c r="E54" s="225" t="n"/>
+      <c r="F54" s="263" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="G54" s="177" t="n"/>
-      <c r="H54" s="256" t="inlineStr">
+      <c r="H54" s="264" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I54" s="257" t="inlineStr"/>
-      <c r="J54" s="254" t="inlineStr">
-        <is>
-          <t>일부는 관련 계정 실증절차에서 테스트됨 → 미테스트 항목 전수 테스트</t>
+      <c r="I54" s="265" t="inlineStr"/>
+      <c r="J54" s="262" t="inlineStr">
+        <is>
+          <t>일부는 관련 계정 실증절차에서 테스트 → 미테스트 항목 전수 테스트</t>
         </is>
       </c>
       <c r="K54" s="125" t="n"/>
@@ -6466,31 +8857,31 @@
       <c r="O54" s="19" t="n"/>
     </row>
     <row r="55" ht="34" customFormat="1" customHeight="1" s="48">
-      <c r="B55" s="253" t="inlineStr">
-        <is>
-          <t>② 비경상·미사용(seldom-used) 계정으로의 분개 (전기오류수정·유형자산처분손실·파생상품손실·영업권 등)</t>
-        </is>
-      </c>
-      <c r="C55" s="226" t="n"/>
-      <c r="D55" s="254" t="inlineStr">
-        <is>
-          <t>연중 사용빈도가 극히 낮은 계정은 비정상 분개의 은닉 통로가 될 수 있음</t>
-        </is>
-      </c>
-      <c r="E55" s="226" t="n"/>
-      <c r="F55" s="255" t="inlineStr">
+      <c r="B55" s="261" t="inlineStr">
+        <is>
+          <t>② 비경상·미사용(seldom-used) 계정 분개(전기오류수정·유형자산처분손실·파생상품손실·영업권 등)</t>
+        </is>
+      </c>
+      <c r="C55" s="225" t="n"/>
+      <c r="D55" s="262" t="inlineStr">
+        <is>
+          <t>사용빈도 극히 낮은 계정은 비정상 분개 은닉 통로 가능</t>
+        </is>
+      </c>
+      <c r="E55" s="225" t="n"/>
+      <c r="F55" s="263" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="G55" s="177" t="n"/>
-      <c r="H55" s="256" t="inlineStr">
+      <c r="H55" s="264" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I55" s="257" t="inlineStr"/>
-      <c r="J55" s="254" t="inlineStr">
+      <c r="I55" s="265" t="inlineStr"/>
+      <c r="J55" s="262" t="inlineStr">
         <is>
           <t>No → 식별 분개 전수 테스트</t>
         </is>
@@ -6502,31 +8893,31 @@
       <c r="O55" s="19" t="n"/>
     </row>
     <row r="56" ht="34" customFormat="1" customHeight="1" s="48">
-      <c r="B56" s="253" t="inlineStr">
+      <c r="B56" s="261" t="inlineStr">
         <is>
           <t>③ 임시·미결산 성격 계정(잡손실·잡이익) 대체분개</t>
         </is>
       </c>
-      <c r="C56" s="226" t="n"/>
-      <c r="D56" s="254" t="inlineStr">
-        <is>
-          <t>손익 조정 목적의 임시계정 이용 가능성 고려</t>
-        </is>
-      </c>
-      <c r="E56" s="226" t="n"/>
-      <c r="F56" s="255" t="inlineStr">
+      <c r="C56" s="225" t="n"/>
+      <c r="D56" s="262" t="inlineStr">
+        <is>
+          <t>손익 조정 목적의 임시계정 이용 가능성</t>
+        </is>
+      </c>
+      <c r="E56" s="225" t="n"/>
+      <c r="F56" s="263" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="G56" s="177" t="n"/>
-      <c r="H56" s="256" t="inlineStr">
+      <c r="H56" s="264" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I56" s="257" t="inlineStr"/>
-      <c r="J56" s="254" t="inlineStr">
+      <c r="I56" s="265" t="inlineStr"/>
+      <c r="J56" s="262" t="inlineStr">
         <is>
           <t>No → 식별 분개 전수 테스트</t>
         </is>
@@ -6538,33 +8929,33 @@
       <c r="O56" s="19" t="n"/>
     </row>
     <row r="57" ht="34" customFormat="1" customHeight="1" s="48">
-      <c r="B57" s="253" t="inlineStr">
-        <is>
-          <t>④ 매출/VFF·충당금 등 유의계정에 대한 기말 조정분개</t>
-        </is>
-      </c>
-      <c r="C57" s="226" t="n"/>
-      <c r="D57" s="254" t="inlineStr">
-        <is>
-          <t>수익인식 및 추정치 조작 위험 고려(ISA 240 수익 추정 부정위험)</t>
-        </is>
-      </c>
-      <c r="E57" s="226" t="n"/>
-      <c r="F57" s="255" t="inlineStr">
+      <c r="B57" s="261" t="inlineStr">
+        <is>
+          <t>④ 매출/VFF·충당금 등 유의계정 기말 조정분개</t>
+        </is>
+      </c>
+      <c r="C57" s="225" t="n"/>
+      <c r="D57" s="262" t="inlineStr">
+        <is>
+          <t>수익인식·추정치 조작 위험(ISA 240)</t>
+        </is>
+      </c>
+      <c r="E57" s="225" t="n"/>
+      <c r="F57" s="263" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="177" t="n"/>
-      <c r="H57" s="256" t="inlineStr">
+      <c r="H57" s="264" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I57" s="257" t="inlineStr"/>
-      <c r="J57" s="254" t="inlineStr">
-        <is>
-          <t>관련 회계추정치 조서(B1-3·C-4·Tax·N2)와 연계 테스트</t>
+      <c r="I57" s="265" t="inlineStr"/>
+      <c r="J57" s="262" t="inlineStr">
+        <is>
+          <t>회계추정치 조서(B1-3·C-4·Tax·N2)와 연계 테스트</t>
         </is>
       </c>
       <c r="K57" s="125" t="n"/>
@@ -6573,11 +8964,11 @@
       <c r="N57" s="19" t="n"/>
       <c r="O57" s="19" t="n"/>
     </row>
-    <row r="58" ht="34" customFormat="1" customHeight="1" s="48">
+    <row r="58" ht="15" customFormat="1" customHeight="1" s="48">
       <c r="B58" s="176" t="n"/>
-      <c r="C58" s="226" t="n"/>
+      <c r="C58" s="225" t="n"/>
       <c r="D58" s="177" t="n"/>
-      <c r="E58" s="226" t="n"/>
+      <c r="E58" s="225" t="n"/>
       <c r="F58" s="177" t="n"/>
       <c r="G58" s="177" t="n"/>
       <c r="H58" s="113" t="n"/>
@@ -6589,11 +8980,11 @@
       <c r="N58" s="19" t="n"/>
       <c r="O58" s="19" t="n"/>
     </row>
-    <row r="59" ht="34" customFormat="1" customHeight="1" s="48">
+    <row r="59" ht="15" customFormat="1" customHeight="1" s="48">
       <c r="B59" s="176" t="n"/>
-      <c r="C59" s="226" t="n"/>
+      <c r="C59" s="225" t="n"/>
       <c r="D59" s="177" t="n"/>
-      <c r="E59" s="226" t="n"/>
+      <c r="E59" s="225" t="n"/>
       <c r="F59" s="177" t="n"/>
       <c r="G59" s="177" t="n"/>
       <c r="H59" s="113" t="n"/>
@@ -6605,11 +8996,11 @@
       <c r="N59" s="19" t="n"/>
       <c r="O59" s="19" t="n"/>
     </row>
-    <row r="60" ht="34" customFormat="1" customHeight="1" s="48">
+    <row r="60" ht="15" customFormat="1" customHeight="1" s="48">
       <c r="B60" s="176" t="n"/>
-      <c r="C60" s="226" t="n"/>
+      <c r="C60" s="225" t="n"/>
       <c r="D60" s="177" t="n"/>
-      <c r="E60" s="226" t="n"/>
+      <c r="E60" s="225" t="n"/>
       <c r="F60" s="177" t="n"/>
       <c r="G60" s="177" t="n"/>
       <c r="H60" s="113" t="n"/>
@@ -6621,11 +9012,11 @@
       <c r="N60" s="19" t="n"/>
       <c r="O60" s="19" t="n"/>
     </row>
-    <row r="61" ht="34" customFormat="1" customHeight="1" s="48">
+    <row r="61" ht="15" customFormat="1" customHeight="1" s="48">
       <c r="B61" s="176" t="n"/>
-      <c r="C61" s="226" t="n"/>
+      <c r="C61" s="225" t="n"/>
       <c r="D61" s="177" t="n"/>
-      <c r="E61" s="226" t="n"/>
+      <c r="E61" s="225" t="n"/>
       <c r="F61" s="177" t="n"/>
       <c r="G61" s="177" t="n"/>
       <c r="H61" s="113" t="n"/>
@@ -6637,11 +9028,11 @@
       <c r="N61" s="19" t="n"/>
       <c r="O61" s="19" t="n"/>
     </row>
-    <row r="62" ht="34" customFormat="1" customHeight="1" s="48">
+    <row r="62" ht="15" customFormat="1" customHeight="1" s="48">
       <c r="B62" s="176" t="n"/>
-      <c r="C62" s="226" t="n"/>
+      <c r="C62" s="225" t="n"/>
       <c r="D62" s="177" t="n"/>
-      <c r="E62" s="226" t="n"/>
+      <c r="E62" s="225" t="n"/>
       <c r="F62" s="177" t="n"/>
       <c r="G62" s="177" t="n"/>
       <c r="H62" s="113" t="n"/>
@@ -6653,11 +9044,11 @@
       <c r="N62" s="19" t="n"/>
       <c r="O62" s="19" t="n"/>
     </row>
-    <row r="63" ht="34" customFormat="1" customHeight="1" s="48" thickBot="1">
+    <row r="63" ht="15.75" customFormat="1" customHeight="1" s="48" thickBot="1">
       <c r="B63" s="200" t="n"/>
-      <c r="C63" s="233" t="n"/>
+      <c r="C63" s="266" t="n"/>
       <c r="D63" s="201" t="n"/>
-      <c r="E63" s="233" t="n"/>
+      <c r="E63" s="266" t="n"/>
       <c r="F63" s="201" t="n"/>
       <c r="G63" s="201" t="n"/>
       <c r="H63" s="127" t="n"/>
@@ -6746,15 +9137,15 @@
           <t>Entries identified in Step 3</t>
         </is>
       </c>
-      <c r="I70" s="258" t="inlineStr">
+      <c r="I70" s="267" t="inlineStr">
         <is>
           <t>In case exeptions are noted:</t>
         </is>
       </c>
-      <c r="J70" s="224" t="n"/>
-      <c r="K70" s="224" t="n"/>
-      <c r="L70" s="224" t="n"/>
-      <c r="M70" s="259" t="n"/>
+      <c r="J70" s="223" t="n"/>
+      <c r="K70" s="223" t="n"/>
+      <c r="L70" s="223" t="n"/>
+      <c r="M70" s="268" t="n"/>
     </row>
     <row r="71" ht="57.95" customFormat="1" customHeight="1" s="10">
       <c r="A71" s="12" t="n"/>
@@ -6828,35 +9219,35 @@
     </row>
     <row r="72" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A72" s="18" t="n"/>
-      <c r="B72" s="260" t="inlineStr">
+      <c r="B72" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C72" s="261" t="inlineStr">
+      <c r="C72" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D72" s="254" t="inlineStr">
+      <c r="D72" s="262" t="inlineStr">
         <is>
           <t>감사조정</t>
         </is>
       </c>
-      <c r="E72" s="254" t="inlineStr">
-        <is>
-          <t>(800000)VFF model income — FY26 감사조정사항_VFF Reclass (영업외→판관)</t>
-        </is>
-      </c>
-      <c r="F72" s="262" t="n">
+      <c r="E72" s="262" t="inlineStr">
+        <is>
+          <t>(800000)VFF model income — FY26 감사조정_VFF Reclass(영업외→판관)</t>
+        </is>
+      </c>
+      <c r="F72" s="271" t="n">
         <v>34966850055</v>
       </c>
-      <c r="G72" s="254" t="inlineStr">
-        <is>
-          <t>Tax .1 / 세무조정</t>
-        </is>
-      </c>
-      <c r="H72" s="263" t="inlineStr">
+      <c r="G72" s="262" t="inlineStr">
+        <is>
+          <t>WTB Adj_2026 / Tax .1</t>
+        </is>
+      </c>
+      <c r="H72" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6869,35 +9260,35 @@
     </row>
     <row r="73" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A73" s="18" t="n"/>
-      <c r="B73" s="260" t="inlineStr">
+      <c r="B73" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C73" s="261" t="inlineStr">
+      <c r="C73" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D73" s="254" t="inlineStr">
+      <c r="D73" s="262" t="inlineStr">
         <is>
           <t>결산(제거)</t>
         </is>
       </c>
-      <c r="E73" s="254" t="inlineStr">
+      <c r="E73" s="262" t="inlineStr">
         <is>
           <t>(185510)ROU Asset Accum — FY26 US 리스분개 제거분개</t>
         </is>
       </c>
-      <c r="F73" s="262" t="n">
+      <c r="F73" s="271" t="n">
         <v>7984693312</v>
       </c>
-      <c r="G73" s="254" t="inlineStr">
+      <c r="G73" s="262" t="inlineStr">
         <is>
           <t>리스 조서</t>
         </is>
       </c>
-      <c r="H73" s="263" t="inlineStr">
+      <c r="H73" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6910,35 +9301,35 @@
     </row>
     <row r="74" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A74" s="18" t="n"/>
-      <c r="B74" s="260" t="inlineStr">
+      <c r="B74" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C74" s="261" t="inlineStr">
+      <c r="C74" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D74" s="254" t="inlineStr">
+      <c r="D74" s="262" t="inlineStr">
         <is>
           <t>감사조정</t>
         </is>
       </c>
-      <c r="E74" s="254" t="inlineStr">
-        <is>
-          <t>지급수수료_기타(KR) — FY25 감사조정사항_DCE 재분류(영업외→판관비)</t>
-        </is>
-      </c>
-      <c r="F74" s="262" t="n">
+      <c r="E74" s="262" t="inlineStr">
+        <is>
+          <t>지급수수료_기타(KR) — FY25 감사조정_DCE 재분류(영업외→판관)</t>
+        </is>
+      </c>
+      <c r="F74" s="271" t="n">
         <v>225732726</v>
       </c>
-      <c r="G74" s="254" t="inlineStr">
-        <is>
-          <t>감사조정 명세</t>
-        </is>
-      </c>
-      <c r="H74" s="263" t="inlineStr">
+      <c r="G74" s="262" t="inlineStr">
+        <is>
+          <t>WTB Adj_2026</t>
+        </is>
+      </c>
+      <c r="H74" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6951,35 +9342,35 @@
     </row>
     <row r="75" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A75" s="18" t="n"/>
-      <c r="B75" s="260" t="inlineStr">
+      <c r="B75" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C75" s="261" t="inlineStr">
+      <c r="C75" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D75" s="254" t="inlineStr">
+      <c r="D75" s="262" t="inlineStr">
         <is>
           <t>감사조정</t>
         </is>
       </c>
-      <c r="E75" s="254" t="inlineStr">
-        <is>
-          <t>수선비(KR) — FY26 감사조정사항_수선비·포장비(원가→판관)</t>
-        </is>
-      </c>
-      <c r="F75" s="262" t="n">
+      <c r="E75" s="262" t="inlineStr">
+        <is>
+          <t>수선비(KR) — FY26 감사조정_수선비·포장비(원가→판관)</t>
+        </is>
+      </c>
+      <c r="F75" s="271" t="n">
         <v>150897377</v>
       </c>
-      <c r="G75" s="254" t="inlineStr">
-        <is>
-          <t>감사조정 명세</t>
-        </is>
-      </c>
-      <c r="H75" s="263" t="inlineStr">
+      <c r="G75" s="262" t="inlineStr">
+        <is>
+          <t>WTB Adj_2026</t>
+        </is>
+      </c>
+      <c r="H75" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6992,35 +9383,35 @@
     </row>
     <row r="76" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A76" s="18" t="n"/>
-      <c r="B76" s="260" t="inlineStr">
+      <c r="B76" s="269" t="inlineStr">
         <is>
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="C76" s="261" t="inlineStr">
+      <c r="C76" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D76" s="254" t="inlineStr">
+      <c r="D76" s="262" t="inlineStr">
         <is>
           <t>수기(비경상)</t>
         </is>
       </c>
-      <c r="E76" s="254" t="inlineStr">
+      <c r="E76" s="262" t="inlineStr">
         <is>
           <t>(730051)파생상품거래손실 — NFD Hedge 5월</t>
         </is>
       </c>
-      <c r="F76" s="262" t="n">
+      <c r="F76" s="271" t="n">
         <v>382583282</v>
       </c>
-      <c r="G76" s="254" t="inlineStr">
+      <c r="G76" s="262" t="inlineStr">
         <is>
           <t>파생상품 조서</t>
         </is>
       </c>
-      <c r="H76" s="263" t="inlineStr">
+      <c r="H76" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -7033,35 +9424,35 @@
     </row>
     <row r="77" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A77" s="18" t="n"/>
-      <c r="B77" s="260" t="inlineStr">
+      <c r="B77" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C77" s="261" t="inlineStr">
+      <c r="C77" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D77" s="254" t="inlineStr">
+      <c r="D77" s="262" t="inlineStr">
         <is>
           <t>재분류</t>
         </is>
       </c>
-      <c r="E77" s="254" t="inlineStr">
-        <is>
-          <t>(664115)유형자산처분손실 — AK원주점 폐점 고정자산 정리</t>
-        </is>
-      </c>
-      <c r="F77" s="262" t="n">
+      <c r="E77" s="262" t="inlineStr">
+        <is>
+          <t>(664115)유형자산처분손실 — AK원주점 폐점 정리</t>
+        </is>
+      </c>
+      <c r="F77" s="271" t="n">
         <v>28699992</v>
       </c>
-      <c r="G77" s="254" t="inlineStr">
+      <c r="G77" s="262" t="inlineStr">
         <is>
           <t>유형자산 조서</t>
         </is>
       </c>
-      <c r="H77" s="263" t="inlineStr">
+      <c r="H77" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -7074,35 +9465,35 @@
     </row>
     <row r="78" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A78" s="18" t="n"/>
-      <c r="B78" s="260" t="inlineStr">
+      <c r="B78" s="269" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C78" s="261" t="inlineStr">
+      <c r="C78" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D78" s="254" t="inlineStr">
+      <c r="D78" s="262" t="inlineStr">
         <is>
           <t>수정분개</t>
         </is>
       </c>
-      <c r="E78" s="254" t="inlineStr">
-        <is>
-          <t>(263500)Lease Liability — Lease entries 수정(2023.9월분 누락)</t>
-        </is>
-      </c>
-      <c r="F78" s="262" t="n">
+      <c r="E78" s="262" t="inlineStr">
+        <is>
+          <t>(263500)Lease Liability — Lease 수정(2023.9월분 누락)</t>
+        </is>
+      </c>
+      <c r="F78" s="271" t="n">
         <v>14800000</v>
       </c>
-      <c r="G78" s="254" t="inlineStr">
+      <c r="G78" s="262" t="inlineStr">
         <is>
           <t>리스 조서</t>
         </is>
       </c>
-      <c r="H78" s="263" t="inlineStr">
+      <c r="H78" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -7115,35 +9506,35 @@
     </row>
     <row r="79" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A79" s="18" t="n"/>
-      <c r="B79" s="260" t="inlineStr">
+      <c r="B79" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C79" s="261" t="inlineStr">
+      <c r="C79" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D79" s="254" t="inlineStr">
+      <c r="D79" s="262" t="inlineStr">
         <is>
           <t>결산</t>
         </is>
       </c>
-      <c r="E79" s="254" t="inlineStr">
+      <c r="E79" s="262" t="inlineStr">
         <is>
           <t>(671030)지급수수료_전문용역 — FY26 딜로이트 세무조정 보수</t>
         </is>
       </c>
-      <c r="F79" s="262" t="n">
+      <c r="F79" s="271" t="n">
         <v>9400000</v>
       </c>
-      <c r="G79" s="254" t="inlineStr">
-        <is>
-          <t>증빙(계약/청구)</t>
-        </is>
-      </c>
-      <c r="H79" s="263" t="inlineStr">
+      <c r="G79" s="262" t="inlineStr">
+        <is>
+          <t>증빙(계약)</t>
+        </is>
+      </c>
+      <c r="H79" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -7156,35 +9547,35 @@
     </row>
     <row r="80" ht="26" customFormat="1" customHeight="1" s="19">
       <c r="A80" s="18" t="n"/>
-      <c r="B80" s="260" t="inlineStr">
+      <c r="B80" s="269" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C80" s="261" t="inlineStr">
+      <c r="C80" s="270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="254" t="inlineStr">
+      <c r="D80" s="262" t="inlineStr">
         <is>
           <t>결산</t>
         </is>
       </c>
-      <c r="E80" s="254" t="inlineStr">
-        <is>
-          <t>(672000)대손상각비/(112000)대손충당금 — 대손충당금 설정</t>
-        </is>
-      </c>
-      <c r="F80" s="262" t="n">
+      <c r="E80" s="262" t="inlineStr">
+        <is>
+          <t>(672000)대손상각비/대손충당금 — 대손충당금 설정</t>
+        </is>
+      </c>
+      <c r="F80" s="271" t="n">
         <v>65944315</v>
       </c>
-      <c r="G80" s="254" t="inlineStr">
+      <c r="G80" s="262" t="inlineStr">
         <is>
           <t>매출채권 조서 B1-3</t>
         </is>
       </c>
-      <c r="H80" s="263" t="inlineStr">
+      <c r="H80" s="272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
